--- a/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
+++ b/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР5_Анализ_конкурентов\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР5_Анализ_конкурентов\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A61359B-42CF-4351-BD41-B199492DD66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FC6CC5-1FCA-4C9A-9ACD-17789CB63EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3157,7 +3157,7 @@
     <t>профессиональные пользователи Excel и моделисты</t>
   </si>
   <si>
-    <t>лицензия на надстройку (цена не показана)</t>
+    <t>лицензия на надстройку (2,75 GBP за пользователя в месяц, срок 12-36 месяцев)</t>
   </si>
   <si>
     <t>Arixcel Explorer: логика формул, сравнение таблиц, карта формул, трассировка зависимых ячеек</t>
@@ -4002,7 +4002,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7D05-44BD-97EB-C8CEC9C15917}"/>
+              <c16:uniqueId val="{00000000-A368-4631-891C-B2BE3B711DFD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4153,7 +4153,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CD55-4B1C-AC29-790E4295FA4C}"/>
+              <c16:uniqueId val="{00000000-C603-477C-95A9-D192FBDBCF22}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4190,7 +4190,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CD55-4B1C-AC29-790E4295FA4C}"/>
+              <c16:uniqueId val="{00000001-C603-477C-95A9-D192FBDBCF22}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4227,7 +4227,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-CD55-4B1C-AC29-790E4295FA4C}"/>
+              <c16:uniqueId val="{00000002-C603-477C-95A9-D192FBDBCF22}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4264,7 +4264,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-CD55-4B1C-AC29-790E4295FA4C}"/>
+              <c16:uniqueId val="{00000003-C603-477C-95A9-D192FBDBCF22}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4301,7 +4301,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-CD55-4B1C-AC29-790E4295FA4C}"/>
+              <c16:uniqueId val="{00000004-C603-477C-95A9-D192FBDBCF22}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4338,7 +4338,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-CD55-4B1C-AC29-790E4295FA4C}"/>
+              <c16:uniqueId val="{00000005-C603-477C-95A9-D192FBDBCF22}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4375,7 +4375,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-CD55-4B1C-AC29-790E4295FA4C}"/>
+              <c16:uniqueId val="{00000006-C603-477C-95A9-D192FBDBCF22}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
+++ b/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР5_Анализ_конкурентов\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FC6CC5-1FCA-4C9A-9ACD-17789CB63EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8064A308-048D-4F6B-BCBD-389C7FC00616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Инструкция" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="1224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1310">
   <si>
     <t>Excel-шаблон анализа конкурентов по сайтам</t>
   </si>
@@ -3415,6 +3415,195 @@
     <t>Присутствует в магазине надстроек</t>
   </si>
   <si>
+    <t>Безопасность</t>
+  </si>
+  <si>
+    <t>https://www.datasnipper.com/security</t>
+  </si>
+  <si>
+    <t>безопасность</t>
+  </si>
+  <si>
+    <t>SOC 2 Type II, Azure, AES-256, TLS 1.2+, хранение до 24 часов, обучение на данных клиентов не ведется, GDPR и AI Act</t>
+  </si>
+  <si>
+    <t>Самый подробный профиль безопасности среди специализированных игроков</t>
+  </si>
+  <si>
+    <t>https://www.datasnipper.com/pricing</t>
+  </si>
+  <si>
+    <t>Start, Accelerate, Elevate без сумм; Book demo и Contact sales</t>
+  </si>
+  <si>
+    <t>Цена по запросу, вход через демо</t>
+  </si>
+  <si>
+    <t>Интеграции</t>
+  </si>
+  <si>
+    <t>https://knowledge.datasnipper.com/en/collections/1449483-integrations</t>
+  </si>
+  <si>
+    <t>интеграции</t>
+  </si>
+  <si>
+    <t>ценность</t>
+  </si>
+  <si>
+    <t>SharePoint, OneDrive, Box, Dropbox, SAP Concur, QuickBooks, Suralink, Azure</t>
+  </si>
+  <si>
+    <t>Интеграции документов аудита, не проверки формул</t>
+  </si>
+  <si>
+    <t>Отзывы Capterra</t>
+  </si>
+  <si>
+    <t>https://www.capterra.com/p/10002513/DataSnipper/</t>
+  </si>
+  <si>
+    <t>4,7 из 5, 131 отзыв, пробной версии нет</t>
+  </si>
+  <si>
+    <t>Сильный репутационный профиль</t>
+  </si>
+  <si>
+    <t>https://datarails.com/pricing/</t>
+  </si>
+  <si>
+    <t>Professional, Premium, Expert без сумм; Request Quote, пробного периода нет</t>
+  </si>
+  <si>
+    <t>Цена по запросу, длинный цикл продажи</t>
+  </si>
+  <si>
+    <t>Центр доверия</t>
+  </si>
+  <si>
+    <t>https://trust.datarails.com/overview</t>
+  </si>
+  <si>
+    <t>SOC 2 Type II, SOC 1, политика информационной безопасности, тест на проникновение; отчеты по запросу</t>
+  </si>
+  <si>
+    <t>Самый полный профиль доверия</t>
+  </si>
+  <si>
+    <t>https://datarails.com/integrations/</t>
+  </si>
+  <si>
+    <t>более 200 интеграций в списке (ERP, CRM, хранилища); на главной заявлено более 600</t>
+  </si>
+  <si>
+    <t>Интеграции - барьер переключения</t>
+  </si>
+  <si>
+    <t>https://www.capterra.com/p/177451/DataRails/</t>
+  </si>
+  <si>
+    <t>4,7 из 5, 245 отзывов</t>
+  </si>
+  <si>
+    <t>Лицензирование</t>
+  </si>
+  <si>
+    <t>https://www.arixcel.com/explorer/download</t>
+  </si>
+  <si>
+    <t>цены</t>
+  </si>
+  <si>
+    <t>2,75 GBP за пользователя в месяц, лицензия 12-36 месяцев, только Windows, пробный режим</t>
+  </si>
+  <si>
+    <t>Цена опубликована, лестницы тарифов нет</t>
+  </si>
+  <si>
+    <t>Цены OAK</t>
+  </si>
+  <si>
+    <t>https://www.operisanalysiskit.com/oak-price/</t>
+  </si>
+  <si>
+    <t>подписка 311,66 GBP в год, более 30 инструментов, Try OAK и Buy now</t>
+  </si>
+  <si>
+    <t>Единичная цена, продажа без консультанта</t>
+  </si>
+  <si>
+    <t>https://shortcut.ai/privacy</t>
+  </si>
+  <si>
+    <t>SOC 2 Type II, AES-256, TLS 1.3, нулевое хранение у провайдеров, SAML, ролевой доступ</t>
+  </si>
+  <si>
+    <t>Безопасность раскрыта в центре приватности</t>
+  </si>
+  <si>
+    <t>Цены и регистрация</t>
+  </si>
+  <si>
+    <t>https://numerous.ai/</t>
+  </si>
+  <si>
+    <t>7 дней бесплатно, оплата за год, 10 USD в месяц, лимит 500 тыс. символов</t>
+  </si>
+  <si>
+    <t>Путь от пробы к подписке без продавца</t>
+  </si>
+  <si>
+    <t>Подвал сайта</t>
+  </si>
+  <si>
+    <t>правовые</t>
+  </si>
+  <si>
+    <t>только политика конфиденциальности и условия, заявлений о безопасности нет</t>
+  </si>
+  <si>
+    <t>Безопасность не раскрыта</t>
+  </si>
+  <si>
+    <t>Отзывы Trustpilot</t>
+  </si>
+  <si>
+    <t>https://www.trustpilot.com/review/numerous.ai</t>
+  </si>
+  <si>
+    <t>2,5 из 5, 5 отзывов, жалобы на автосписание после пробного периода</t>
+  </si>
+  <si>
+    <t>Риск политики пробного периода</t>
+  </si>
+  <si>
+    <t>Пробный период</t>
+  </si>
+  <si>
+    <t>https://www.perfectxl.com/products/perfectxl-formula-inspector/free-trial-vdependents/</t>
+  </si>
+  <si>
+    <t>пробный доступ</t>
+  </si>
+  <si>
+    <t>вход</t>
+  </si>
+  <si>
+    <t>30 дней без карты и автопродления, Excel 2016 и новее</t>
+  </si>
+  <si>
+    <t>Бесплатный вход есть</t>
+  </si>
+  <si>
+    <t>Правовые страницы</t>
+  </si>
+  <si>
+    <t>https://www.perfectxl.com/legal/privacy-policy/</t>
+  </si>
+  <si>
+    <t>политика конфиденциальности, условия, cookie; страницы безопасности нет</t>
+  </si>
+  <si>
     <t>PerfectXL Suite: Risk Finder, Explore, Compare, Highlighter,</t>
   </si>
   <si>
@@ -3481,6 +3670,21 @@
     <t>корпоративные пакеты</t>
   </si>
   <si>
+    <t>Подсветка проблемных ячеек в файле</t>
+  </si>
+  <si>
+    <t>продуктовые страницы</t>
+  </si>
+  <si>
+    <t>Оценка рисков и здоровья модели</t>
+  </si>
+  <si>
+    <t>Библиотека правил проверки</t>
+  </si>
+  <si>
+    <t>страницы продукта и принципов</t>
+  </si>
+  <si>
     <t>Arixcel Explorer: логика формул, сравнение таблиц, карта фор</t>
   </si>
   <si>
@@ -3505,15 +3709,33 @@
     <t>Интеграции и API</t>
   </si>
   <si>
-    <t>интеграции</t>
-  </si>
-  <si>
     <t>Автоматическое исправление ошибок</t>
   </si>
   <si>
     <t>страница агента</t>
   </si>
   <si>
+    <t>Работа в Google Sheets</t>
+  </si>
+  <si>
+    <t>главная и интеграции</t>
+  </si>
+  <si>
+    <t>Политика хранения и удаления данных</t>
+  </si>
+  <si>
+    <t>Ролевой доступ в команде</t>
+  </si>
+  <si>
+    <t>страницы безопасности и цен</t>
+  </si>
+  <si>
+    <t>Журнал изменений и трассировка источников</t>
+  </si>
+  <si>
+    <t>страницы безопасности и продукта</t>
+  </si>
+  <si>
     <t xml:space="preserve">FinanceOS: FP&amp;A, закрытие месяца, денежные потоки, контроль </t>
   </si>
   <si>
@@ -3523,9 +3745,18 @@
     <t>заявления о проверяемости</t>
   </si>
   <si>
+    <t>Интеграции с ERP и учетными системами</t>
+  </si>
+  <si>
+    <t>страница интеграций</t>
+  </si>
+  <si>
     <t xml:space="preserve">агентная автоматизация аудита, надстройка Excel, извлечение </t>
   </si>
   <si>
+    <t>Извлечение данных из документов</t>
+  </si>
+  <si>
     <t>найти ошибки до отправки файла</t>
   </si>
   <si>
@@ -3581,6 +3812,33 @@
   </si>
   <si>
     <t>не править вручную</t>
+  </si>
+  <si>
+    <t>увидеть ошибки прямо в таблице</t>
+  </si>
+  <si>
+    <t>понять общий уровень риска файла</t>
+  </si>
+  <si>
+    <t>проверять по известным принципам моделирования</t>
+  </si>
+  <si>
+    <t>использовать сервис вне Excel</t>
+  </si>
+  <si>
+    <t>получать данные из учета без выгрузки</t>
+  </si>
+  <si>
+    <t>знать, сколько хранится файл</t>
+  </si>
+  <si>
+    <t>разграничить права пользователей</t>
+  </si>
+  <si>
+    <t>проследить каждое изменение и источник</t>
+  </si>
+  <si>
+    <t>сверить таблицу с первичными документами</t>
   </si>
   <si>
     <t>04_Кано</t>
@@ -3980,16 +4238,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -4002,7 +4260,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A368-4631-891C-B2BE3B711DFD}"/>
+              <c16:uniqueId val="{00000000-F59D-49D5-BD25-EC558622C0AC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4153,7 +4411,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C603-477C-95A9-D192FBDBCF22}"/>
+              <c16:uniqueId val="{00000000-22E9-406A-86E3-0504545CEBE1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4190,7 +4448,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C603-477C-95A9-D192FBDBCF22}"/>
+              <c16:uniqueId val="{00000001-22E9-406A-86E3-0504545CEBE1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4227,7 +4485,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C603-477C-95A9-D192FBDBCF22}"/>
+              <c16:uniqueId val="{00000002-22E9-406A-86E3-0504545CEBE1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4264,7 +4522,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C603-477C-95A9-D192FBDBCF22}"/>
+              <c16:uniqueId val="{00000003-22E9-406A-86E3-0504545CEBE1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4301,7 +4559,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-C603-477C-95A9-D192FBDBCF22}"/>
+              <c16:uniqueId val="{00000004-22E9-406A-86E3-0504545CEBE1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4338,7 +4596,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-C603-477C-95A9-D192FBDBCF22}"/>
+              <c16:uniqueId val="{00000005-22E9-406A-86E3-0504545CEBE1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4375,7 +4633,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-C603-477C-95A9-D192FBDBCF22}"/>
+              <c16:uniqueId val="{00000006-22E9-406A-86E3-0504545CEBE1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5253,11 +5511,11 @@
       </c>
       <c r="G5" s="2">
         <f>COUNTIF('04_Кано'!$E$7:$E$206,F5)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" ref="H5:H10" si="0">IFERROR(G5/SUM($G$5:$G$10),"")</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>367</v>
@@ -5277,7 +5535,7 @@
       </c>
       <c r="B6" s="8">
         <f>COUNTIF('02_Карта_сайтов'!$C$7:$C$206,"?*")</f>
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>962</v>
@@ -5290,11 +5548,11 @@
       </c>
       <c r="G6" s="2">
         <f>COUNTIF('04_Кано'!$E$7:$E$206,F6)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" si="0"/>
-        <v>0.4375</v>
+        <v>0.44</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>374</v>
@@ -5314,7 +5572,7 @@
       </c>
       <c r="B7" s="8">
         <f>COUNTIF('03_Левитт'!$E$7:$E$306,"?*")</f>
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>965</v>
@@ -5327,22 +5585,22 @@
       </c>
       <c r="G7" s="2">
         <f>COUNTIF('04_Кано'!$E$7:$E$206,F7)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>378</v>
       </c>
       <c r="K7" s="2">
         <f>COUNTIF('03_Левитт'!$D$7:$D$306,J7)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L7" s="2">
         <f>IFERROR(AVERAGEIF('03_Левитт'!$D$7:$D$306,J7,'03_Левитт'!$L$7:$L$306),"")</f>
-        <v>3.7111111111111104</v>
+        <v>3.6885714285714282</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25.5">
@@ -5351,7 +5609,7 @@
       </c>
       <c r="B8" s="8">
         <f>COUNTIF('04_Кано'!$B$7:$B$206,"?*")</f>
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>968</v>
@@ -5364,22 +5622,22 @@
       </c>
       <c r="G8" s="2">
         <f>COUNTIF('04_Кано'!$E$7:$E$206,F8)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" s="5">
         <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <v>0.16</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>387</v>
       </c>
       <c r="K8" s="2">
         <f>COUNTIF('03_Левитт'!$D$7:$D$306,J8)</f>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L8" s="2">
         <f>IFERROR(AVERAGEIF('03_Левитт'!$D$7:$D$306,J8,'03_Левитт'!$L$7:$L$306),"")</f>
-        <v>2.6312500000000001</v>
+        <v>2.5662857142857143</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -5412,11 +5670,11 @@
       </c>
       <c r="K9" s="2">
         <f>COUNTIF('03_Левитт'!$D$7:$D$306,J9)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L9" s="2">
         <f>IFERROR(AVERAGEIF('03_Левитт'!$D$7:$D$306,J9,'03_Левитт'!$L$7:$L$306),"")</f>
-        <v>3.3333333333333335</v>
+        <v>2.7912499999999998</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15">
@@ -5425,7 +5683,7 @@
       </c>
       <c r="B10" s="8">
         <f>COUNTIF('07_Стандарт_рынка'!$I$7:$I$206,"Зона дифференциации")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>972</v>
@@ -7299,197 +7557,517 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+    <row r="23" spans="1:10" ht="38.25">
+      <c r="A23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G23" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="25.5">
+      <c r="A24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="25.5">
+      <c r="A25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I25" s="2">
+        <v>4</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>1136</v>
+      </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G26" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I26" s="2">
+        <v>5</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="25.5">
+      <c r="A27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I27" s="2">
+        <v>5</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="38.25">
+      <c r="A28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G28" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I28" s="2">
+        <v>5</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="25.5">
+      <c r="A29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I29" s="2">
+        <v>4</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>1150</v>
+      </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G30" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="38.25">
+      <c r="A31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G31" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I31" s="2">
+        <v>5</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="25.5">
+      <c r="A32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G32" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I32" s="2">
+        <v>5</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="38.25">
+      <c r="A33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G33" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="25.5">
+      <c r="A34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="25.5">
+      <c r="A35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G35" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I35" s="2">
+        <v>4</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="25.5">
+      <c r="A36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G36" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I36" s="2">
+        <v>5</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="25.5">
+      <c r="A37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G37" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I37" s="2">
+        <v>5</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="25.5">
+      <c r="A38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46298</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I38" s="2">
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>1172</v>
+      </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2"/>
@@ -9632,7 +10210,7 @@
         <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1024</v>
@@ -9641,13 +10219,13 @@
         <v>367</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1124</v>
+        <v>1187</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1125</v>
+        <v>1188</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -9676,7 +10254,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>1024</v>
@@ -9685,13 +10263,13 @@
         <v>387</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1127</v>
+        <v>1190</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1128</v>
+        <v>1191</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -9720,7 +10298,7 @@
         <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1024</v>
@@ -9729,13 +10307,13 @@
         <v>387</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1129</v>
+        <v>1192</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1130</v>
+        <v>1193</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -9764,7 +10342,7 @@
         <v>81</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>1024</v>
@@ -9773,13 +10351,13 @@
         <v>378</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1131</v>
+        <v>1194</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1132</v>
+        <v>1195</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -9808,7 +10386,7 @@
         <v>81</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>1024</v>
@@ -9817,13 +10395,13 @@
         <v>374</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1133</v>
+        <v>1196</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1134</v>
+        <v>1197</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -9852,7 +10430,7 @@
         <v>81</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>1024</v>
@@ -9861,13 +10439,13 @@
         <v>378</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1135</v>
+        <v>1198</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1136</v>
+        <v>1199</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -9896,7 +10474,7 @@
         <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>1024</v>
@@ -9905,13 +10483,13 @@
         <v>378</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1137</v>
+        <v>1200</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1138</v>
+        <v>1201</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -9940,7 +10518,7 @@
         <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>1024</v>
@@ -9949,13 +10527,13 @@
         <v>378</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1139</v>
+        <v>1202</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1140</v>
+        <v>1203</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -9984,7 +10562,7 @@
         <v>81</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>1024</v>
@@ -9993,13 +10571,13 @@
         <v>387</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1141</v>
+        <v>1204</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1142</v>
+        <v>1205</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -10028,7 +10606,7 @@
         <v>81</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1123</v>
+        <v>1186</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>1024</v>
@@ -10037,13 +10615,13 @@
         <v>387</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1143</v>
+        <v>1206</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1144</v>
+        <v>1207</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -10069,25 +10647,25 @@
     </row>
     <row r="17" spans="1:14" ht="25.5">
       <c r="A17" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1145</v>
+        <v>1186</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1124</v>
+        <v>1208</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1125</v>
+        <v>1209</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -10099,39 +10677,39 @@
         <v>3</v>
       </c>
       <c r="K17" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2">
         <f t="shared" si="0"/>
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="M17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N17" s="2"/>
     </row>
     <row r="18" spans="1:14" ht="25.5">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1145</v>
+        <v>1186</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1127</v>
+        <v>1210</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1128</v>
+        <v>1209</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -10143,11 +10721,11 @@
         <v>3</v>
       </c>
       <c r="K18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="M18" s="2" t="str">
         <f t="shared" si="1"/>
@@ -10157,25 +10735,25 @@
     </row>
     <row r="19" spans="1:14" ht="25.5">
       <c r="A19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1145</v>
+        <v>1186</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1129</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1130</v>
+        <v>1212</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -10204,22 +10782,22 @@
         <v>83</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1145</v>
+        <v>1213</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1034</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1134</v>
+        <v>1188</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -10248,7 +10826,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1145</v>
+        <v>1213</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>1034</v>
@@ -10257,57 +10835,57 @@
         <v>387</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1141</v>
+        <v>1190</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1142</v>
+        <v>1191</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
       </c>
       <c r="I21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3.33</v>
       </c>
       <c r="M21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Слабый признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="1:14" ht="25.5">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1146</v>
+        <v>1213</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1124</v>
+        <v>1192</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1125</v>
+        <v>1193</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -10319,39 +10897,39 @@
         <v>3</v>
       </c>
       <c r="K22" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2">
         <f t="shared" si="0"/>
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="M22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N22" s="2"/>
     </row>
     <row r="23" spans="1:14" ht="25.5">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1146</v>
+        <v>1213</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1127</v>
+        <v>1196</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1128</v>
+        <v>1197</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -10363,83 +10941,83 @@
         <v>3</v>
       </c>
       <c r="K23" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>4.17</v>
       </c>
       <c r="M23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N23" s="2"/>
     </row>
     <row r="24" spans="1:14" ht="25.5">
       <c r="A24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1146</v>
+        <v>1213</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1131</v>
+        <v>1204</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1132</v>
+        <v>1205</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
       </c>
       <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
         <v>2</v>
       </c>
-      <c r="J24" s="2">
-        <v>3</v>
-      </c>
       <c r="K24" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Слабый признак</v>
       </c>
       <c r="N24" s="2"/>
     </row>
     <row r="25" spans="1:14" ht="25.5">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1146</v>
+        <v>1213</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1133</v>
+        <v>1208</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1134</v>
+        <v>1209</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -10451,15 +11029,15 @@
         <v>3</v>
       </c>
       <c r="K25" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2">
         <f t="shared" si="0"/>
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="M25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -10468,22 +11046,22 @@
         <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1146</v>
+        <v>1214</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>1040</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1139</v>
+        <v>1187</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1140</v>
+        <v>1188</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -10495,15 +11073,15 @@
         <v>3</v>
       </c>
       <c r="K26" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>4.17</v>
       </c>
       <c r="M26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -10512,7 +11090,7 @@
         <v>84</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1146</v>
+        <v>1214</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>1040</v>
@@ -10521,13 +11099,13 @@
         <v>387</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1141</v>
+        <v>1190</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1142</v>
+        <v>1191</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -10539,39 +11117,39 @@
         <v>3</v>
       </c>
       <c r="K27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2">
         <f t="shared" si="0"/>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="M27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Слабый признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N27" s="2"/>
     </row>
     <row r="28" spans="1:14" ht="25.5">
       <c r="A28" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1127</v>
+        <v>1194</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1128</v>
+        <v>1195</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -10597,25 +11175,25 @@
     </row>
     <row r="29" spans="1:14" ht="25.5">
       <c r="A29" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>374</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1133</v>
+        <v>1196</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1134</v>
+        <v>1197</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -10641,25 +11219,25 @@
     </row>
     <row r="30" spans="1:14" ht="25.5">
       <c r="A30" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1147</v>
+        <v>1202</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1070</v>
+        <v>1203</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -10671,11 +11249,11 @@
         <v>3</v>
       </c>
       <c r="K30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="M30" s="2" t="str">
         <f t="shared" si="1"/>
@@ -10685,25 +11263,25 @@
     </row>
     <row r="31" spans="1:14" ht="25.5">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>1149</v>
+        <v>1205</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -10715,83 +11293,83 @@
         <v>3</v>
       </c>
       <c r="K31" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>1.67</v>
       </c>
       <c r="M31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Слабый признак</v>
       </c>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" ht="25.5">
       <c r="A32" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1150</v>
+        <v>1210</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1151</v>
+        <v>1209</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
       </c>
       <c r="I32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2">
         <v>3</v>
       </c>
       <c r="K32" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M32" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="1:14" ht="25.5">
       <c r="A33" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1135</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1136</v>
+        <v>1212</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -10826,22 +11404,22 @@
         <v>1046</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1137</v>
+        <v>1190</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1138</v>
+        <v>1191</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
       </c>
       <c r="I34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2">
         <v>3</v>
@@ -10851,11 +11429,11 @@
       </c>
       <c r="L34" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="M34" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -10870,16 +11448,16 @@
         <v>1046</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1152</v>
+        <v>1196</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>1153</v>
+        <v>1197</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -10891,15 +11469,15 @@
         <v>3</v>
       </c>
       <c r="K35" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L35" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="M35" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -10914,16 +11492,16 @@
         <v>1046</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1139</v>
+        <v>1215</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1140</v>
+        <v>1070</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -10935,11 +11513,11 @@
         <v>3</v>
       </c>
       <c r="K36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="M36" s="2" t="str">
         <f t="shared" si="1"/>
@@ -10961,13 +11539,13 @@
         <v>387</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1143</v>
+        <v>1216</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1144</v>
+        <v>1217</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -10979,11 +11557,11 @@
         <v>3</v>
       </c>
       <c r="K37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="M37" s="2" t="str">
         <f t="shared" si="1"/>
@@ -11002,60 +11580,60 @@
         <v>1046</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1154</v>
+        <v>1218</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1155</v>
+        <v>1219</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
       </c>
       <c r="I38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" s="2">
         <v>3</v>
       </c>
       <c r="K38" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L38" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>5</v>
       </c>
       <c r="M38" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N38" s="2"/>
     </row>
     <row r="39" spans="1:14" ht="25.5">
       <c r="A39" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1133</v>
+        <v>1198</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>1134</v>
+        <v>1199</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
@@ -11067,83 +11645,83 @@
         <v>3</v>
       </c>
       <c r="K39" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2">
         <f t="shared" si="0"/>
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="M39" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N39" s="2"/>
     </row>
     <row r="40" spans="1:14" ht="25.5">
       <c r="A40" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1147</v>
+        <v>1200</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1070</v>
+        <v>1201</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H40" s="2">
         <v>1</v>
       </c>
       <c r="I40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J40" s="2">
         <v>3</v>
       </c>
       <c r="K40" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N40" s="2"/>
     </row>
     <row r="41" spans="1:14" ht="25.5">
       <c r="A41" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1148</v>
+        <v>1220</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1149</v>
+        <v>1133</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
@@ -11155,11 +11733,11 @@
         <v>3</v>
       </c>
       <c r="K41" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="M41" s="2" t="str">
         <f t="shared" si="1"/>
@@ -11169,25 +11747,25 @@
     </row>
     <row r="42" spans="1:14" ht="25.5">
       <c r="A42" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>378</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1135</v>
+        <v>1202</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>1136</v>
+        <v>1203</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H42" s="2">
         <v>1</v>
@@ -11213,69 +11791,69 @@
     </row>
     <row r="43" spans="1:14" ht="25.5">
       <c r="A43" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1137</v>
+        <v>1206</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1138</v>
+        <v>1207</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H43" s="2">
         <v>1</v>
       </c>
       <c r="I43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" s="2">
         <v>3</v>
       </c>
       <c r="K43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="M43" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="25.5">
       <c r="A44" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1141</v>
+        <v>1221</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>1142</v>
+        <v>1222</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H44" s="2">
         <v>1</v>
@@ -11287,39 +11865,39 @@
         <v>3</v>
       </c>
       <c r="K44" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L44" s="2">
         <f t="shared" si="0"/>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="M44" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Слабый признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N44" s="2"/>
     </row>
     <row r="45" spans="1:14" ht="25.5">
       <c r="A45" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1143</v>
+        <v>1223</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1144</v>
+        <v>1224</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H45" s="2">
         <v>1</v>
@@ -11331,39 +11909,39 @@
         <v>3</v>
       </c>
       <c r="K45" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="M45" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Слабый признак</v>
       </c>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" spans="1:14" ht="38.25">
+    <row r="46" spans="1:14" ht="25.5">
       <c r="A46" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1156</v>
+        <v>1051</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>378</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1131</v>
+        <v>1225</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1132</v>
+        <v>1219</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H46" s="2">
         <v>1</v>
@@ -11387,27 +11965,27 @@
       </c>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="1:14" ht="38.25">
+    <row r="47" spans="1:14" ht="25.5">
       <c r="A47" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1156</v>
+        <v>1051</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1133</v>
+        <v>1226</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>1134</v>
+        <v>1227</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H47" s="2">
         <v>1</v>
@@ -11419,39 +11997,39 @@
         <v>3</v>
       </c>
       <c r="K47" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2">
         <f t="shared" si="0"/>
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="M47" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N47" s="2"/>
     </row>
-    <row r="48" spans="1:14" ht="38.25">
+    <row r="48" spans="1:14" ht="25.5">
       <c r="A48" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1156</v>
+        <v>1051</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1147</v>
+        <v>1228</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>1070</v>
+        <v>1229</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H48" s="2">
         <v>1</v>
@@ -11463,11 +12041,11 @@
         <v>3</v>
       </c>
       <c r="K48" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L48" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="M48" s="2" t="str">
         <f t="shared" si="1"/>
@@ -11475,27 +12053,27 @@
       </c>
       <c r="N48" s="2"/>
     </row>
-    <row r="49" spans="1:14" ht="38.25">
+    <row r="49" spans="1:14" ht="25.5">
       <c r="A49" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1156</v>
+        <v>1057</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1148</v>
+        <v>1196</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>1149</v>
+        <v>1197</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H49" s="2">
         <v>1</v>
@@ -11507,51 +12085,51 @@
         <v>3</v>
       </c>
       <c r="K49" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L49" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>4.17</v>
       </c>
       <c r="M49" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N49" s="2"/>
     </row>
-    <row r="50" spans="1:14" ht="38.25">
+    <row r="50" spans="1:14" ht="25.5">
       <c r="A50" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1156</v>
+        <v>1057</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1157</v>
+        <v>1215</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>1158</v>
+        <v>1070</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H50" s="2">
         <v>1</v>
       </c>
       <c r="I50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2">
         <f t="shared" si="0"/>
@@ -11563,27 +12141,27 @@
       </c>
       <c r="N50" s="2"/>
     </row>
-    <row r="51" spans="1:14" ht="38.25">
+    <row r="51" spans="1:14" ht="25.5">
       <c r="A51" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1156</v>
+        <v>1057</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1150</v>
+        <v>1216</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>1151</v>
+        <v>1217</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H51" s="2">
         <v>1</v>
@@ -11595,55 +12173,55 @@
         <v>3</v>
       </c>
       <c r="K51" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L51" s="2">
         <f t="shared" si="0"/>
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="M51" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N51" s="2"/>
     </row>
-    <row r="52" spans="1:14" ht="38.25">
+    <row r="52" spans="1:14" ht="25.5">
       <c r="A52" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1156</v>
+        <v>1057</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1152</v>
+        <v>1198</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>1153</v>
+        <v>1199</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H52" s="2">
         <v>1</v>
       </c>
       <c r="I52" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2">
         <v>3</v>
       </c>
       <c r="K52" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L52" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="M52" s="2" t="str">
         <f t="shared" si="1"/>
@@ -11651,27 +12229,27 @@
       </c>
       <c r="N52" s="2"/>
     </row>
-    <row r="53" spans="1:14" ht="38.25">
+    <row r="53" spans="1:14" ht="25.5">
       <c r="A53" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1156</v>
+        <v>1057</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>378</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1139</v>
+        <v>1200</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1140</v>
+        <v>1201</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
@@ -11695,27 +12273,27 @@
       </c>
       <c r="N53" s="2"/>
     </row>
-    <row r="54" spans="1:14" ht="38.25">
+    <row r="54" spans="1:14" ht="25.5">
       <c r="A54" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1156</v>
+        <v>1057</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1141</v>
+        <v>1204</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>1142</v>
+        <v>1205</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H54" s="2">
         <v>1</v>
@@ -11739,27 +12317,27 @@
       </c>
       <c r="N54" s="2"/>
     </row>
-    <row r="55" spans="1:14" ht="38.25">
+    <row r="55" spans="1:14" ht="25.5">
       <c r="A55" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1156</v>
+        <v>1057</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1143</v>
+        <v>1206</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>1144</v>
+        <v>1207</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H55" s="2">
         <v>1</v>
@@ -11785,25 +12363,25 @@
     </row>
     <row r="56" spans="1:14" ht="25.5">
       <c r="A56" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1159</v>
+        <v>1057</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1131</v>
+        <v>1223</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>1132</v>
+        <v>1224</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H56" s="2">
         <v>1</v>
@@ -11815,39 +12393,39 @@
         <v>3</v>
       </c>
       <c r="K56" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>1.67</v>
       </c>
       <c r="M56" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Слабый признак</v>
       </c>
       <c r="N56" s="2"/>
     </row>
-    <row r="57" spans="1:14" ht="25.5">
+    <row r="57" spans="1:14" ht="38.25">
       <c r="A57" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1133</v>
+        <v>1194</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>1134</v>
+        <v>1195</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H57" s="2">
         <v>1</v>
@@ -11859,39 +12437,39 @@
         <v>3</v>
       </c>
       <c r="K57" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L57" s="2">
         <f t="shared" si="0"/>
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="M57" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N57" s="2"/>
     </row>
-    <row r="58" spans="1:14" ht="25.5">
+    <row r="58" spans="1:14" ht="38.25">
       <c r="A58" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>374</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1147</v>
+        <v>1196</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>1070</v>
+        <v>1197</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H58" s="2">
         <v>1</v>
@@ -11903,39 +12481,39 @@
         <v>3</v>
       </c>
       <c r="K58" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L58" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="M58" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N58" s="2"/>
     </row>
-    <row r="59" spans="1:14" ht="25.5">
+    <row r="59" spans="1:14" ht="38.25">
       <c r="A59" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1148</v>
+        <v>1215</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>1149</v>
+        <v>1070</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H59" s="2">
         <v>1</v>
@@ -11947,11 +12525,11 @@
         <v>3</v>
       </c>
       <c r="K59" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" si="0"/>
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="M59" s="2" t="str">
         <f t="shared" si="1"/>
@@ -11959,27 +12537,27 @@
       </c>
       <c r="N59" s="2"/>
     </row>
-    <row r="60" spans="1:14" ht="25.5">
+    <row r="60" spans="1:14" ht="38.25">
       <c r="A60" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1157</v>
+        <v>1216</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>1158</v>
+        <v>1217</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H60" s="2">
         <v>1</v>
@@ -11991,83 +12569,83 @@
         <v>3</v>
       </c>
       <c r="K60" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60" s="2">
         <f t="shared" si="0"/>
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="M60" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N60" s="2"/>
     </row>
-    <row r="61" spans="1:14" ht="25.5">
+    <row r="61" spans="1:14" ht="38.25">
       <c r="A61" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1150</v>
+        <v>1231</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>1151</v>
+        <v>1232</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H61" s="2">
         <v>1</v>
       </c>
       <c r="I61" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J61" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K61" s="2">
         <v>5</v>
       </c>
       <c r="L61" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M61" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N61" s="2"/>
     </row>
-    <row r="62" spans="1:14" ht="25.5">
+    <row r="62" spans="1:14" ht="38.25">
       <c r="A62" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1152</v>
+        <v>1218</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>1153</v>
+        <v>1219</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H62" s="2">
         <v>1</v>
@@ -12079,39 +12657,39 @@
         <v>3</v>
       </c>
       <c r="K62" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L62" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="M62" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N62" s="2"/>
     </row>
-    <row r="63" spans="1:14" ht="25.5">
+    <row r="63" spans="1:14" ht="38.25">
       <c r="A63" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1139</v>
+        <v>1220</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H63" s="2">
         <v>1</v>
@@ -12123,83 +12701,83 @@
         <v>3</v>
       </c>
       <c r="K63" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M63" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Сильный признак</v>
+        <v>Рабочий признак</v>
       </c>
       <c r="N63" s="2"/>
     </row>
-    <row r="64" spans="1:14" ht="25.5">
+    <row r="64" spans="1:14" ht="38.25">
       <c r="A64" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1141</v>
+        <v>1202</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>1142</v>
+        <v>1203</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H64" s="2">
         <v>1</v>
       </c>
       <c r="I64" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J64" s="2">
         <v>3</v>
       </c>
       <c r="K64" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L64" s="2">
         <f t="shared" si="0"/>
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="M64" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Слабый признак</v>
+        <v>Сильный признак</v>
       </c>
       <c r="N64" s="2"/>
     </row>
-    <row r="65" spans="1:14" ht="25.5">
+    <row r="65" spans="1:14" ht="38.25">
       <c r="A65" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1159</v>
+        <v>1230</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>387</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1143</v>
+        <v>1204</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>1144</v>
+        <v>1205</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1126</v>
+        <v>1189</v>
       </c>
       <c r="H65" s="2">
         <v>1</v>
@@ -12211,433 +12789,851 @@
         <v>3</v>
       </c>
       <c r="K65" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="M65" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Рабочий признак</v>
+        <v>Слабый признак</v>
       </c>
       <c r="N65" s="2"/>
     </row>
-    <row r="66" spans="1:14">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2" t="str">
+    <row r="66" spans="1:14" ht="38.25">
+      <c r="A66" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H66" s="2">
+        <v>1</v>
+      </c>
+      <c r="I66" s="2">
+        <v>2</v>
+      </c>
+      <c r="J66" s="2">
+        <v>3</v>
+      </c>
+      <c r="K66" s="2">
+        <v>3</v>
+      </c>
+      <c r="L66" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="M66" s="2" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N66" s="2"/>
     </row>
-    <row r="67" spans="1:14">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2" t="str">
+    <row r="67" spans="1:14" ht="38.25">
+      <c r="A67" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H67" s="2">
+        <v>1</v>
+      </c>
+      <c r="I67" s="2">
+        <v>2</v>
+      </c>
+      <c r="J67" s="2">
+        <v>3</v>
+      </c>
+      <c r="K67" s="2">
+        <v>2</v>
+      </c>
+      <c r="L67" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1.67</v>
       </c>
       <c r="M67" s="2" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Слабый признак</v>
       </c>
       <c r="N67" s="2"/>
     </row>
-    <row r="68" spans="1:14">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2" t="str">
+    <row r="68" spans="1:14" ht="38.25">
+      <c r="A68" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2">
+        <v>3</v>
+      </c>
+      <c r="J68" s="2">
+        <v>3</v>
+      </c>
+      <c r="K68" s="2">
+        <v>2</v>
+      </c>
+      <c r="L68" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N68" s="2"/>
     </row>
-    <row r="69" spans="1:14">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2" t="str">
+    <row r="69" spans="1:14" ht="38.25">
+      <c r="A69" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H69" s="2">
+        <v>1</v>
+      </c>
+      <c r="I69" s="2">
+        <v>2</v>
+      </c>
+      <c r="J69" s="2">
+        <v>3</v>
+      </c>
+      <c r="K69" s="2">
+        <v>4</v>
+      </c>
+      <c r="L69" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.33</v>
       </c>
       <c r="M69" s="2" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N69" s="2"/>
     </row>
-    <row r="70" spans="1:14">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" s="2" t="str">
+    <row r="70" spans="1:14" ht="38.25">
+      <c r="A70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H70" s="2">
+        <v>1</v>
+      </c>
+      <c r="I70" s="2">
+        <v>2</v>
+      </c>
+      <c r="J70" s="2">
+        <v>3</v>
+      </c>
+      <c r="K70" s="2">
+        <v>3</v>
+      </c>
+      <c r="L70" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="M70" s="2" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N70" s="2"/>
     </row>
-    <row r="71" spans="1:14">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2" t="str">
+    <row r="71" spans="1:14" ht="25.5">
+      <c r="A71" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H71" s="2">
+        <v>1</v>
+      </c>
+      <c r="I71" s="2">
+        <v>2</v>
+      </c>
+      <c r="J71" s="2">
+        <v>3</v>
+      </c>
+      <c r="K71" s="2">
+        <v>4</v>
+      </c>
+      <c r="L71" s="2">
         <f t="shared" ref="L71:L134" si="2">IF(OR(H71="",I71="",J71="",K71=""),"",ROUND(H71*((I71+J71)/6)*K71,2))</f>
-        <v/>
+        <v>3.33</v>
       </c>
       <c r="M71" s="2" t="str">
         <f t="shared" ref="M71:M134" si="3">IF(L71="","",IF(AND(L71&gt;=3.5,H71=1),"Сильный признак",IF(AND(L71&gt;=2,H71=1),"Рабочий признак",IF(H71=1,"Слабый признак","Отсутствует"))))</f>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N71" s="2"/>
     </row>
-    <row r="72" spans="1:14">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2" t="str">
+    <row r="72" spans="1:14" ht="25.5">
+      <c r="A72" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H72" s="2">
+        <v>1</v>
+      </c>
+      <c r="I72" s="2">
+        <v>2</v>
+      </c>
+      <c r="J72" s="2">
+        <v>3</v>
+      </c>
+      <c r="K72" s="2">
+        <v>5</v>
+      </c>
+      <c r="L72" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.17</v>
       </c>
       <c r="M72" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Сильный признак</v>
       </c>
       <c r="N72" s="2"/>
     </row>
-    <row r="73" spans="1:14">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2" t="str">
+    <row r="73" spans="1:14" ht="25.5">
+      <c r="A73" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H73" s="2">
+        <v>1</v>
+      </c>
+      <c r="I73" s="2">
+        <v>2</v>
+      </c>
+      <c r="J73" s="2">
+        <v>3</v>
+      </c>
+      <c r="K73" s="2">
+        <v>3</v>
+      </c>
+      <c r="L73" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="M73" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N73" s="2"/>
     </row>
-    <row r="74" spans="1:14">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2" t="str">
+    <row r="74" spans="1:14" ht="25.5">
+      <c r="A74" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H74" s="2">
+        <v>1</v>
+      </c>
+      <c r="I74" s="2">
+        <v>2</v>
+      </c>
+      <c r="J74" s="2">
+        <v>3</v>
+      </c>
+      <c r="K74" s="2">
+        <v>4</v>
+      </c>
+      <c r="L74" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3.33</v>
       </c>
       <c r="M74" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N74" s="2"/>
     </row>
-    <row r="75" spans="1:14">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2" t="str">
+    <row r="75" spans="1:14" ht="25.5">
+      <c r="A75" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H75" s="2">
+        <v>1</v>
+      </c>
+      <c r="I75" s="2">
+        <v>2</v>
+      </c>
+      <c r="J75" s="2">
+        <v>3</v>
+      </c>
+      <c r="K75" s="2">
+        <v>5</v>
+      </c>
+      <c r="L75" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.17</v>
       </c>
       <c r="M75" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Сильный признак</v>
       </c>
       <c r="N75" s="2"/>
     </row>
-    <row r="76" spans="1:14">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2" t="str">
+    <row r="76" spans="1:14" ht="25.5">
+      <c r="A76" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H76" s="2">
+        <v>1</v>
+      </c>
+      <c r="I76" s="2">
+        <v>3</v>
+      </c>
+      <c r="J76" s="2">
+        <v>3</v>
+      </c>
+      <c r="K76" s="2">
+        <v>5</v>
+      </c>
+      <c r="L76" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M76" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Сильный признак</v>
       </c>
       <c r="N76" s="2"/>
     </row>
-    <row r="77" spans="1:14">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2" t="str">
+    <row r="77" spans="1:14" ht="25.5">
+      <c r="A77" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H77" s="2">
+        <v>1</v>
+      </c>
+      <c r="I77" s="2">
+        <v>2</v>
+      </c>
+      <c r="J77" s="2">
+        <v>3</v>
+      </c>
+      <c r="K77" s="2">
+        <v>3</v>
+      </c>
+      <c r="L77" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="M77" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N77" s="2"/>
     </row>
-    <row r="78" spans="1:14">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2" t="str">
+    <row r="78" spans="1:14" ht="25.5">
+      <c r="A78" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H78" s="2">
+        <v>1</v>
+      </c>
+      <c r="I78" s="2">
+        <v>3</v>
+      </c>
+      <c r="J78" s="2">
+        <v>3</v>
+      </c>
+      <c r="K78" s="2">
+        <v>4</v>
+      </c>
+      <c r="L78" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M78" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Сильный признак</v>
       </c>
       <c r="N78" s="2"/>
     </row>
-    <row r="79" spans="1:14">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2" t="str">
+    <row r="79" spans="1:14" ht="25.5">
+      <c r="A79" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H79" s="2">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2">
+        <v>2</v>
+      </c>
+      <c r="J79" s="2">
+        <v>3</v>
+      </c>
+      <c r="K79" s="2">
+        <v>2</v>
+      </c>
+      <c r="L79" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.67</v>
       </c>
       <c r="M79" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Слабый признак</v>
       </c>
       <c r="N79" s="2"/>
     </row>
-    <row r="80" spans="1:14">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2" t="str">
+    <row r="80" spans="1:14" ht="25.5">
+      <c r="A80" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H80" s="2">
+        <v>1</v>
+      </c>
+      <c r="I80" s="2">
+        <v>2</v>
+      </c>
+      <c r="J80" s="2">
+        <v>3</v>
+      </c>
+      <c r="K80" s="2">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="M80" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N80" s="2"/>
     </row>
-    <row r="81" spans="1:14">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2" t="str">
+    <row r="81" spans="1:14" ht="25.5">
+      <c r="A81" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H81" s="2">
+        <v>1</v>
+      </c>
+      <c r="I81" s="2">
+        <v>2</v>
+      </c>
+      <c r="J81" s="2">
+        <v>3</v>
+      </c>
+      <c r="K81" s="2">
+        <v>2</v>
+      </c>
+      <c r="L81" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.67</v>
       </c>
       <c r="M81" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Слабый признак</v>
       </c>
       <c r="N81" s="2"/>
     </row>
-    <row r="82" spans="1:14">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2" t="str">
+    <row r="82" spans="1:14" ht="25.5">
+      <c r="A82" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H82" s="2">
+        <v>1</v>
+      </c>
+      <c r="I82" s="2">
+        <v>3</v>
+      </c>
+      <c r="J82" s="2">
+        <v>3</v>
+      </c>
+      <c r="K82" s="2">
+        <v>4</v>
+      </c>
+      <c r="L82" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Сильный признак</v>
       </c>
       <c r="N82" s="2"/>
     </row>
-    <row r="83" spans="1:14">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2" t="str">
+    <row r="83" spans="1:14" ht="25.5">
+      <c r="A83" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H83" s="2">
+        <v>1</v>
+      </c>
+      <c r="I83" s="2">
+        <v>2</v>
+      </c>
+      <c r="J83" s="2">
+        <v>3</v>
+      </c>
+      <c r="K83" s="2">
+        <v>4</v>
+      </c>
+      <c r="L83" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3.33</v>
       </c>
       <c r="M83" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N83" s="2"/>
     </row>
-    <row r="84" spans="1:14">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2" t="str">
+    <row r="84" spans="1:14" ht="25.5">
+      <c r="A84" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H84" s="2">
+        <v>1</v>
+      </c>
+      <c r="I84" s="2">
+        <v>3</v>
+      </c>
+      <c r="J84" s="2">
+        <v>3</v>
+      </c>
+      <c r="K84" s="2">
+        <v>2</v>
+      </c>
+      <c r="L84" s="2">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Рабочий признак</v>
       </c>
       <c r="N84" s="2"/>
     </row>
@@ -17661,13 +18657,13 @@
         <v>152</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1124</v>
+        <v>1187</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1160</v>
+        <v>1237</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1125</v>
+        <v>1188</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>375</v>
@@ -17690,7 +18686,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1161</v>
+        <v>1238</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -17700,13 +18696,13 @@
         <v>153</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1127</v>
+        <v>1190</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1162</v>
+        <v>1239</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1128</v>
+        <v>1191</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>371</v>
@@ -17729,7 +18725,7 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1163</v>
+        <v>1240</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -17739,13 +18735,13 @@
         <v>154</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1129</v>
+        <v>1192</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1164</v>
+        <v>1241</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1130</v>
+        <v>1193</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>371</v>
@@ -17768,7 +18764,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>1165</v>
+        <v>1242</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -17778,13 +18774,13 @@
         <v>155</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1131</v>
+        <v>1194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1166</v>
+        <v>1243</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1132</v>
+        <v>1195</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>371</v>
@@ -17807,7 +18803,7 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1163</v>
+        <v>1240</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -17817,13 +18813,13 @@
         <v>156</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1133</v>
+        <v>1196</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1167</v>
+        <v>1244</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1134</v>
+        <v>1197</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>375</v>
@@ -17846,7 +18842,7 @@
         <v>Минимальный рыночный стандарт</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1161</v>
+        <v>1238</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -17856,10 +18852,10 @@
         <v>157</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1147</v>
+        <v>1215</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1168</v>
+        <v>1245</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>1070</v>
@@ -17885,7 +18881,7 @@
         <v>Переходит в ожидаемую норму</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1163</v>
+        <v>1240</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -17895,13 +18891,13 @@
         <v>158</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1148</v>
+        <v>1216</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1169</v>
+        <v>1246</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1149</v>
+        <v>1217</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>394</v>
@@ -17924,7 +18920,7 @@
         <v>Переходит в ожидаемую норму</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1163</v>
+        <v>1240</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -17934,13 +18930,13 @@
         <v>159</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1157</v>
+        <v>1231</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1170</v>
+        <v>1247</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1158</v>
+        <v>1232</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>394</v>
@@ -17963,7 +18959,7 @@
         <v>Зона дифференциации</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1165</v>
+        <v>1242</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -17973,13 +18969,13 @@
         <v>160</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1150</v>
+        <v>1218</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1171</v>
+        <v>1248</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1151</v>
+        <v>1219</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>375</v>
@@ -18002,7 +18998,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>1161</v>
+        <v>1238</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -18012,13 +19008,13 @@
         <v>161</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1135</v>
+        <v>1198</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1172</v>
+        <v>1249</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1136</v>
+        <v>1199</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>375</v>
@@ -18041,7 +19037,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1161</v>
+        <v>1238</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -18051,13 +19047,13 @@
         <v>162</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1137</v>
+        <v>1200</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1173</v>
+        <v>1250</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1138</v>
+        <v>1201</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>371</v>
@@ -18080,7 +19076,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1163</v>
+        <v>1240</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -18090,13 +19086,13 @@
         <v>163</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1152</v>
+        <v>1220</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1174</v>
+        <v>1251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1153</v>
+        <v>1133</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>371</v>
@@ -18119,7 +19115,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>1163</v>
+        <v>1240</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -18129,13 +19125,13 @@
         <v>164</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1139</v>
+        <v>1202</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1175</v>
+        <v>1252</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1140</v>
+        <v>1203</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>371</v>
@@ -18158,7 +19154,7 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>1161</v>
+        <v>1238</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -18168,13 +19164,13 @@
         <v>165</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1141</v>
+        <v>1204</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1176</v>
+        <v>1253</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1142</v>
+        <v>1205</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>970</v>
@@ -18197,7 +19193,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>1161</v>
+        <v>1238</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -18207,13 +19203,13 @@
         <v>166</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1143</v>
+        <v>1206</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1177</v>
+        <v>1254</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1144</v>
+        <v>1207</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>371</v>
@@ -18236,7 +19232,7 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1161</v>
+        <v>1238</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -18246,13 +19242,13 @@
         <v>167</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1154</v>
+        <v>1221</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1178</v>
+        <v>1255</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1155</v>
+        <v>1222</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>394</v>
@@ -18275,7 +19271,7 @@
         <v>Зона дифференциации</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1165</v>
+        <v>1242</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -18284,22 +19280,38 @@
       <c r="A23" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="5" t="str">
+      <c r="B23" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5">
         <f>IF(G23="","",IFERROR(G23/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I23" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I23" s="2">
+        <v>3.5</v>
+      </c>
       <c r="J23" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K23" s="2"/>
+        <v>Зона усиления ценности</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>1242</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
@@ -18307,45 +19319,77 @@
       <c r="A24" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="5" t="str">
+      <c r="B24" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3</v>
+      </c>
+      <c r="G24" s="2">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5">
         <f>IF(G24="","",IFERROR(G24/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I24" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I24" s="2">
+        <v>3.5</v>
+      </c>
       <c r="J24" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K24" s="2"/>
+        <v>Зона дифференциации</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>1242</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" ht="25.5">
       <c r="A25" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="5" t="str">
+      <c r="B25" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5">
         <f>IF(G25="","",IFERROR(G25/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I25" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I25" s="2">
+        <v>3.5</v>
+      </c>
       <c r="J25" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K25" s="2"/>
+        <v>Зона усиления ценности</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>1242</v>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
     </row>
@@ -18353,45 +19397,77 @@
       <c r="A26" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="5" t="str">
+      <c r="B26" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F26" s="2">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2">
+        <v>3</v>
+      </c>
+      <c r="H26" s="5">
         <f>IF(G26="","",IFERROR(G26/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I26" s="2"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="I26" s="2">
+        <v>3.33</v>
+      </c>
       <c r="J26" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K26" s="2"/>
+        <v>Не делать при дефиците ресурсов</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>1240</v>
+      </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" ht="25.5">
       <c r="A27" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="5" t="str">
+      <c r="B27" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F27" s="2">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5">
         <f>IF(G27="","",IFERROR(G27/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I27" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I27" s="2">
+        <v>4</v>
+      </c>
       <c r="J27" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K27" s="2"/>
+        <v>Не делать при дефиците ресурсов</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>1242</v>
+      </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
@@ -18399,22 +19475,38 @@
       <c r="A28" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="5" t="str">
+      <c r="B28" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F28" s="2">
+        <v>4</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3</v>
+      </c>
+      <c r="H28" s="5">
         <f>IF(G28="","",IFERROR(G28/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I28" s="2"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="I28" s="2">
+        <v>4.33</v>
+      </c>
       <c r="J28" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K28" s="2"/>
+        <v>Потенциальный обязательный разрыв</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>1238</v>
+      </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
@@ -18422,68 +19514,116 @@
       <c r="A29" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="5" t="str">
+      <c r="B29" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5">
         <f>IF(G29="","",IFERROR(G29/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I29" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I29" s="2">
+        <v>4</v>
+      </c>
       <c r="J29" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K29" s="2"/>
+        <v>Зона усиления ценности</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>1242</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" ht="25.5">
       <c r="A30" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="5" t="str">
+      <c r="B30" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F30" s="2">
+        <v>4</v>
+      </c>
+      <c r="G30" s="2">
+        <v>2</v>
+      </c>
+      <c r="H30" s="5">
         <f>IF(G30="","",IFERROR(G30/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I30" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I30" s="2">
+        <v>4</v>
+      </c>
       <c r="J30" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K30" s="2"/>
+        <v>Зона усиления ценности</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>1242</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" ht="25.5">
       <c r="A31" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="5" t="str">
+      <c r="B31" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F31" s="2">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5">
         <f>IF(G31="","",IFERROR(G31/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="I31" s="2"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I31" s="2">
+        <v>5</v>
+      </c>
       <c r="J31" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K31" s="2"/>
+        <v>Не делать при дефиците ресурсов</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>1242</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
@@ -22669,10 +23809,10 @@
         <v>366</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1202</v>
+        <v>1288</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1203</v>
+        <v>1289</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>367</v>
@@ -22695,10 +23835,10 @@
         <v>370</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1204</v>
+        <v>1290</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1205</v>
+        <v>1291</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>367</v>
@@ -22721,10 +23861,10 @@
         <v>373</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1206</v>
+        <v>1292</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1207</v>
+        <v>1293</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>374</v>
@@ -22747,10 +23887,10 @@
         <v>377</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1208</v>
+        <v>1294</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1209</v>
+        <v>1295</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>378</v>
@@ -22773,10 +23913,10 @@
         <v>380</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1210</v>
+        <v>1296</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1207</v>
+        <v>1293</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>378</v>
@@ -22799,10 +23939,10 @@
         <v>382</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1211</v>
+        <v>1297</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1212</v>
+        <v>1298</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>378</v>
@@ -22825,7 +23965,7 @@
         <v>384</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1213</v>
+        <v>1299</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>165</v>
@@ -22851,10 +23991,10 @@
         <v>386</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1214</v>
+        <v>1300</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1215</v>
+        <v>1301</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>387</v>
@@ -22877,10 +24017,10 @@
         <v>390</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1216</v>
+        <v>1302</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1217</v>
+        <v>1303</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>387</v>
@@ -22903,10 +24043,10 @@
         <v>392</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1218</v>
+        <v>1304</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1219</v>
+        <v>1305</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>393</v>
@@ -22929,10 +24069,10 @@
         <v>396</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1220</v>
+        <v>1306</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1221</v>
+        <v>1307</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>397</v>
@@ -22955,10 +24095,10 @@
         <v>400</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1222</v>
+        <v>1308</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1223</v>
+        <v>1309</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>401</v>
@@ -26623,10 +27763,10 @@
         <v>537</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1124</v>
+        <v>1187</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>367</v>
@@ -26657,10 +27797,10 @@
         <v>538</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1127</v>
+        <v>1190</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>387</v>
@@ -26691,10 +27831,10 @@
         <v>539</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1129</v>
+        <v>1192</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>387</v>
@@ -26725,10 +27865,10 @@
         <v>540</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1131</v>
+        <v>1194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>378</v>
@@ -26759,10 +27899,10 @@
         <v>541</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1133</v>
+        <v>1196</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>374</v>
@@ -26793,10 +27933,10 @@
         <v>542</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1147</v>
+        <v>1215</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>374</v>
@@ -26827,10 +27967,10 @@
         <v>543</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1148</v>
+        <v>1216</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>387</v>
@@ -26861,10 +28001,10 @@
         <v>544</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1157</v>
+        <v>1231</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>393</v>
@@ -26895,10 +28035,10 @@
         <v>545</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1150</v>
+        <v>1218</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>378</v>
@@ -26929,10 +28069,10 @@
         <v>546</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1135</v>
+        <v>1198</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>378</v>
@@ -26963,10 +28103,10 @@
         <v>547</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1137</v>
+        <v>1200</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>378</v>
@@ -26997,10 +28137,10 @@
         <v>548</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1152</v>
+        <v>1220</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>387</v>
@@ -27031,10 +28171,10 @@
         <v>549</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1139</v>
+        <v>1202</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>378</v>
@@ -27065,10 +28205,10 @@
         <v>550</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1141</v>
+        <v>1204</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>387</v>
@@ -27099,10 +28239,10 @@
         <v>551</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1143</v>
+        <v>1206</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>387</v>
@@ -27133,10 +28273,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1154</v>
+        <v>1221</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1179</v>
+        <v>1265</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>393</v>
@@ -27166,19 +28306,31 @@
       <c r="A23" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="5" t="str">
+      <c r="B23" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F23" s="2">
+        <v>2</v>
+      </c>
+      <c r="G23" s="5">
         <f>IF(F23="","",IFERROR(F23/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H23" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H23" s="2">
+        <v>3.5</v>
+      </c>
       <c r="I23" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Проверить необходимость</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -27188,19 +28340,31 @@
       <c r="A24" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="5" t="str">
+      <c r="B24" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2</v>
+      </c>
+      <c r="G24" s="5">
         <f>IF(F24="","",IFERROR(F24/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H24" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H24" s="2">
+        <v>3.5</v>
+      </c>
       <c r="I24" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Зона дифференциации</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -27210,19 +28374,31 @@
       <c r="A25" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="5" t="str">
+      <c r="B25" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F25" s="2">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5">
         <f>IF(F25="","",IFERROR(F25/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H25" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H25" s="2">
+        <v>3.5</v>
+      </c>
       <c r="I25" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Проверить необходимость</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -27232,19 +28408,31 @@
       <c r="A26" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="5" t="str">
+      <c r="B26" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F26" s="2">
+        <v>3</v>
+      </c>
+      <c r="G26" s="5">
         <f>IF(F26="","",IFERROR(F26/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H26" s="2"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H26" s="2">
+        <v>3.33</v>
+      </c>
       <c r="I26" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Низкий приоритет</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -27254,19 +28442,31 @@
       <c r="A27" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="5" t="str">
+      <c r="B27" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F27" s="2">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5">
         <f>IF(F27="","",IFERROR(F27/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H27" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4</v>
+      </c>
       <c r="I27" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Низкий приоритет</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -27276,19 +28476,31 @@
       <c r="A28" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="5" t="str">
+      <c r="B28" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3</v>
+      </c>
+      <c r="G28" s="5">
         <f>IF(F28="","",IFERROR(F28/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H28" s="2"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H28" s="2">
+        <v>4.33</v>
+      </c>
       <c r="I28" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Формирующаяся норма</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -27298,41 +28510,65 @@
       <c r="A29" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="5" t="str">
+      <c r="B29" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F29" s="2">
+        <v>2</v>
+      </c>
+      <c r="G29" s="5">
         <f>IF(F29="","",IFERROR(F29/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H29" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H29" s="2">
+        <v>4</v>
+      </c>
       <c r="I29" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Проверить необходимость</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" ht="25.5">
       <c r="A30" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="5" t="str">
+      <c r="B30" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2</v>
+      </c>
+      <c r="G30" s="5">
         <f>IF(F30="","",IFERROR(F30/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H30" s="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H30" s="2">
+        <v>4</v>
+      </c>
       <c r="I30" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Проверить необходимость</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -27342,19 +28578,31 @@
       <c r="A31" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="5" t="str">
+      <c r="B31" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5">
         <f>IF(F31="","",IFERROR(F31/MAX(1,COUNTIF('01_Конкуренты'!$B$7:$B$36,"?*")),""))</f>
-        <v/>
-      </c>
-      <c r="H31" s="2"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="H31" s="2">
+        <v>5</v>
+      </c>
       <c r="I31" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Низкий приоритет</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -31379,10 +32627,10 @@
         <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1180</v>
+        <v>1266</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1181</v>
+        <v>1267</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -31410,7 +32658,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1182</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25.5">
@@ -31421,15 +32669,15 @@
         <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1183</v>
+        <v>1269</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1184</v>
+        <v>1270</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>1185</v>
+        <v>1271</v>
       </c>
       <c r="H8" s="2">
         <v>3</v>
@@ -31452,7 +32700,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1182</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25.5">
@@ -31463,15 +32711,15 @@
         <v>85</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1186</v>
+        <v>1272</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1187</v>
+        <v>1273</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>1188</v>
+        <v>1274</v>
       </c>
       <c r="H9" s="2">
         <v>2</v>
@@ -31494,7 +32742,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1182</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25.5">
@@ -31505,10 +32753,10 @@
         <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1189</v>
+        <v>1275</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1190</v>
+        <v>1276</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -31536,7 +32784,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1182</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25.5">
@@ -31547,15 +32795,15 @@
         <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1191</v>
+        <v>1277</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1192</v>
+        <v>1278</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>1193</v>
+        <v>1279</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -31578,7 +32826,7 @@
         <v>Слабое преимущество</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1182</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25.5">
@@ -31589,15 +32837,15 @@
         <v>87</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1194</v>
+        <v>1280</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1195</v>
+        <v>1281</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>1196</v>
+        <v>1282</v>
       </c>
       <c r="H12" s="2">
         <v>4</v>
@@ -31620,7 +32868,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1182</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25.5">
@@ -31631,10 +32879,10 @@
         <v>88</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1197</v>
+        <v>1283</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1198</v>
+        <v>1284</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -31662,7 +32910,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1182</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25.5">
@@ -31673,15 +32921,15 @@
         <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1199</v>
+        <v>1285</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1200</v>
+        <v>1286</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>1201</v>
+        <v>1287</v>
       </c>
       <c r="H14" s="2">
         <v>5</v>
@@ -31704,7 +32952,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1182</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="15" spans="1:14">

--- a/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
+++ b/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР5_Анализ_конкурентов\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-89518d\ЛР5_Анализ_конкурентов\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8064A308-048D-4F6B-BCBD-389C7FC00616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F7AE98-6B56-41B8-8DFC-25FB36ABA8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1327">
   <si>
     <t>Excel-шаблон анализа конкурентов по сайтам</t>
   </si>
@@ -3760,79 +3760,130 @@
     <t>найти ошибки до отправки файла</t>
   </si>
   <si>
+    <t>включить в MVP (ядро проверки)</t>
+  </si>
+  <si>
+    <t>понять, как считается результат</t>
+  </si>
+  <si>
+    <t>рассмотреть во втором релизе</t>
+  </si>
+  <si>
+    <t>увидеть, что изменилось</t>
+  </si>
+  <si>
+    <t>рассмотреть как дифференциацию после MVP</t>
+  </si>
+  <si>
+    <t>передать результат проверки</t>
+  </si>
+  <si>
+    <t>включить в MVP в базовой форме, экспорт - во втором релизе</t>
+  </si>
+  <si>
+    <t>работать в привычной среде</t>
+  </si>
+  <si>
+    <t>включить в релиз 3 (бета v1); в MVP его заменяет веб-аудит</t>
+  </si>
+  <si>
+    <t>быстро проверить файл</t>
+  </si>
+  <si>
+    <t>реализовано в MVP: веб-аудит без установки</t>
+  </si>
+  <si>
+    <t>понять причину и исправление</t>
+  </si>
+  <si>
+    <t>рассмотреть для релиза 3 после проверки спроса (AI-пояснения)</t>
+  </si>
+  <si>
+    <t>довериться результату проверки</t>
+  </si>
+  <si>
+    <t>включить в MVP как ядро дифференциации</t>
+  </si>
+  <si>
+    <t>безопасно загружать файлы</t>
+  </si>
+  <si>
     <t>включить в MVP</t>
   </si>
   <si>
-    <t>понять, как считается результат</t>
-  </si>
-  <si>
-    <t>включить во второй релиз</t>
-  </si>
-  <si>
-    <t>увидеть, что изменилось</t>
+    <t>попробовать без обязательств</t>
+  </si>
+  <si>
+    <t>включить в MVP (бесплатный тариф)</t>
+  </si>
+  <si>
+    <t>понять цену до разговора с продавцом</t>
+  </si>
+  <si>
+    <t>включить в MVP (страница тарифов)</t>
+  </si>
+  <si>
+    <t>встроить проверку в процесс</t>
+  </si>
+  <si>
+    <t>рассмотреть после проверки спроса (API)</t>
+  </si>
+  <si>
+    <t>убедиться в надежности поставщика</t>
+  </si>
+  <si>
+    <t>включить в MVP (примеры найденных ошибок, первые отзывы)</t>
+  </si>
+  <si>
+    <t>освоить продукт без помощи</t>
+  </si>
+  <si>
+    <t>включить в MVP в минимальной форме (справка)</t>
+  </si>
+  <si>
+    <t>работать группой</t>
+  </si>
+  <si>
+    <t>включить в релиз Team (следующий релиз)</t>
+  </si>
+  <si>
+    <t>не править вручную</t>
+  </si>
+  <si>
+    <t>увидеть ошибки прямо в таблице</t>
   </si>
   <si>
     <t>рассмотреть как дифференциацию</t>
   </si>
   <si>
-    <t>передать результат проверки</t>
-  </si>
-  <si>
-    <t>работать в привычной среде</t>
-  </si>
-  <si>
-    <t>быстро проверить файл</t>
-  </si>
-  <si>
-    <t>понять причину и исправление</t>
-  </si>
-  <si>
-    <t>довериться результату проверки</t>
-  </si>
-  <si>
-    <t>безопасно загружать файлы</t>
-  </si>
-  <si>
-    <t>попробовать без обязательств</t>
-  </si>
-  <si>
-    <t>понять цену до разговора с продавцом</t>
-  </si>
-  <si>
-    <t>встроить проверку в процесс</t>
-  </si>
-  <si>
-    <t>убедиться в надежности поставщика</t>
-  </si>
-  <si>
-    <t>освоить продукт без помощи</t>
-  </si>
-  <si>
-    <t>работать группой</t>
-  </si>
-  <si>
-    <t>не править вручную</t>
-  </si>
-  <si>
-    <t>увидеть ошибки прямо в таблице</t>
-  </si>
-  <si>
     <t>понять общий уровень риска файла</t>
   </si>
   <si>
     <t>проверять по известным принципам моделирования</t>
   </si>
   <si>
+    <t>рассмотреть как дифференциацию (шаблоны правил)</t>
+  </si>
+  <si>
     <t>использовать сервис вне Excel</t>
   </si>
   <si>
+    <t>не делать (вне границ ПЗ1)</t>
+  </si>
+  <si>
     <t>получать данные из учета без выгрузки</t>
   </si>
   <si>
+    <t>не делать при дефиците ресурсов</t>
+  </si>
+  <si>
     <t>знать, сколько хранится файл</t>
   </si>
   <si>
     <t>разграничить права пользователей</t>
+  </si>
+  <si>
+    <t>включить в релиз Team</t>
   </si>
   <si>
     <t>проследить каждое изменение и источник</t>
@@ -4260,7 +4311,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F59D-49D5-BD25-EC558622C0AC}"/>
+              <c16:uniqueId val="{00000000-A414-4B5A-9EA4-A33B837B2866}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4411,7 +4462,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000000-3E41-4EE9-842B-76EDCA87612D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4448,7 +4499,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000001-3E41-4EE9-842B-76EDCA87612D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4485,7 +4536,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000002-3E41-4EE9-842B-76EDCA87612D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4522,7 +4573,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000003-3E41-4EE9-842B-76EDCA87612D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4559,7 +4610,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000004-3E41-4EE9-842B-76EDCA87612D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4596,7 +4647,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000005-3E41-4EE9-842B-76EDCA87612D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4633,7 +4684,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000006-3E41-4EE9-842B-76EDCA87612D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18730,7 +18781,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" ht="25.5">
       <c r="A9" s="2" t="s">
         <v>154</v>
       </c>
@@ -18769,7 +18820,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" ht="25.5">
       <c r="A10" s="2" t="s">
         <v>155</v>
       </c>
@@ -18803,12 +18854,12 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" ht="25.5">
       <c r="A11" s="2" t="s">
         <v>156</v>
       </c>
@@ -18816,7 +18867,7 @@
         <v>1196</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>1197</v>
@@ -18842,12 +18893,12 @@
         <v>Минимальный рыночный стандарт</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" ht="25.5">
       <c r="A12" s="2" t="s">
         <v>157</v>
       </c>
@@ -18855,7 +18906,7 @@
         <v>1215</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>1070</v>
@@ -18881,12 +18932,12 @@
         <v>Переходит в ожидаемую норму</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" ht="25.5">
       <c r="A13" s="2" t="s">
         <v>158</v>
       </c>
@@ -18894,7 +18945,7 @@
         <v>1216</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>1217</v>
@@ -18920,7 +18971,7 @@
         <v>Переходит в ожидаемую норму</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -18933,7 +18984,7 @@
         <v>1231</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>1232</v>
@@ -18959,7 +19010,7 @@
         <v>Зона дифференциации</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1242</v>
+        <v>1252</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -18972,7 +19023,7 @@
         <v>1218</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>1219</v>
@@ -18998,7 +19049,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>1238</v>
+        <v>1254</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -19011,7 +19062,7 @@
         <v>1198</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>1199</v>
@@ -19037,7 +19088,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1238</v>
+        <v>1256</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -19050,7 +19101,7 @@
         <v>1200</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>1201</v>
@@ -19076,7 +19127,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1240</v>
+        <v>1258</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -19089,7 +19140,7 @@
         <v>1220</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>1133</v>
@@ -19115,12 +19166,12 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" ht="25.5">
       <c r="A19" s="2" t="s">
         <v>164</v>
       </c>
@@ -19128,7 +19179,7 @@
         <v>1202</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1252</v>
+        <v>1261</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>1203</v>
@@ -19154,12 +19205,12 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" ht="25.5">
       <c r="A20" s="2" t="s">
         <v>165</v>
       </c>
@@ -19167,7 +19218,7 @@
         <v>1204</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1253</v>
+        <v>1263</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>1205</v>
@@ -19193,7 +19244,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>1238</v>
+        <v>1264</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -19206,7 +19257,7 @@
         <v>1206</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1254</v>
+        <v>1265</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>1207</v>
@@ -19232,12 +19283,12 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1238</v>
+        <v>1266</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" ht="25.5">
       <c r="A22" s="2" t="s">
         <v>167</v>
       </c>
@@ -19245,7 +19296,7 @@
         <v>1221</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1255</v>
+        <v>1267</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1222</v>
@@ -19284,7 +19335,7 @@
         <v>1208</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1256</v>
+        <v>1268</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>1209</v>
@@ -19310,7 +19361,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1242</v>
+        <v>1269</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -19323,7 +19374,7 @@
         <v>1210</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1257</v>
+        <v>1270</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>1209</v>
@@ -19349,7 +19400,7 @@
         <v>Зона дифференциации</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1242</v>
+        <v>1269</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -19362,7 +19413,7 @@
         <v>1211</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>1212</v>
@@ -19388,7 +19439,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>1242</v>
+        <v>1272</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -19401,7 +19452,7 @@
         <v>1223</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1259</v>
+        <v>1273</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>1224</v>
@@ -19427,7 +19478,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>1240</v>
+        <v>1274</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -19440,7 +19491,7 @@
         <v>1233</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1260</v>
+        <v>1275</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>1234</v>
@@ -19466,7 +19517,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>1242</v>
+        <v>1276</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -19479,7 +19530,7 @@
         <v>1225</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1261</v>
+        <v>1277</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>1219</v>
@@ -19505,7 +19556,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1238</v>
+        <v>1254</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -19518,7 +19569,7 @@
         <v>1226</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1262</v>
+        <v>1278</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>1227</v>
@@ -19544,7 +19595,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>1242</v>
+        <v>1279</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -19557,7 +19608,7 @@
         <v>1228</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1263</v>
+        <v>1280</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>1229</v>
@@ -19583,7 +19634,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>1242</v>
+        <v>1269</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -19596,7 +19647,7 @@
         <v>1236</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1264</v>
+        <v>1281</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>1191</v>
@@ -19622,7 +19673,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>1242</v>
+        <v>1276</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -23809,10 +23860,10 @@
         <v>366</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1288</v>
+        <v>1305</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1289</v>
+        <v>1306</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>367</v>
@@ -23835,10 +23886,10 @@
         <v>370</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1290</v>
+        <v>1307</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1291</v>
+        <v>1308</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>367</v>
@@ -23861,10 +23912,10 @@
         <v>373</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1292</v>
+        <v>1309</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1293</v>
+        <v>1310</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>374</v>
@@ -23887,10 +23938,10 @@
         <v>377</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1294</v>
+        <v>1311</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1295</v>
+        <v>1312</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>378</v>
@@ -23913,10 +23964,10 @@
         <v>380</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1296</v>
+        <v>1313</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1293</v>
+        <v>1310</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>378</v>
@@ -23939,10 +23990,10 @@
         <v>382</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1297</v>
+        <v>1314</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1298</v>
+        <v>1315</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>378</v>
@@ -23965,7 +24016,7 @@
         <v>384</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1299</v>
+        <v>1316</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>165</v>
@@ -23991,10 +24042,10 @@
         <v>386</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1300</v>
+        <v>1317</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1301</v>
+        <v>1318</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>387</v>
@@ -24017,10 +24068,10 @@
         <v>390</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1302</v>
+        <v>1319</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1303</v>
+        <v>1320</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>387</v>
@@ -24043,10 +24094,10 @@
         <v>392</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1304</v>
+        <v>1321</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1305</v>
+        <v>1322</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>393</v>
@@ -24069,10 +24120,10 @@
         <v>396</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1306</v>
+        <v>1323</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1307</v>
+        <v>1324</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>397</v>
@@ -24095,10 +24146,10 @@
         <v>400</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1308</v>
+        <v>1325</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1309</v>
+        <v>1326</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>401</v>
@@ -27766,7 +27817,7 @@
         <v>1187</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>367</v>
@@ -27800,7 +27851,7 @@
         <v>1190</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>387</v>
@@ -27834,7 +27885,7 @@
         <v>1192</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>387</v>
@@ -27868,7 +27919,7 @@
         <v>1194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>378</v>
@@ -27902,7 +27953,7 @@
         <v>1196</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>374</v>
@@ -27936,7 +27987,7 @@
         <v>1215</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>374</v>
@@ -27970,7 +28021,7 @@
         <v>1216</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>387</v>
@@ -28004,7 +28055,7 @@
         <v>1231</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>393</v>
@@ -28038,7 +28089,7 @@
         <v>1218</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>378</v>
@@ -28072,7 +28123,7 @@
         <v>1198</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>378</v>
@@ -28106,7 +28157,7 @@
         <v>1200</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>378</v>
@@ -28140,7 +28191,7 @@
         <v>1220</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>387</v>
@@ -28174,7 +28225,7 @@
         <v>1202</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>378</v>
@@ -28208,7 +28259,7 @@
         <v>1204</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>387</v>
@@ -28242,7 +28293,7 @@
         <v>1206</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>387</v>
@@ -28276,7 +28327,7 @@
         <v>1221</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>393</v>
@@ -28310,7 +28361,7 @@
         <v>1208</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>387</v>
@@ -28344,7 +28395,7 @@
         <v>1210</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>387</v>
@@ -28378,7 +28429,7 @@
         <v>1211</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>387</v>
@@ -28412,7 +28463,7 @@
         <v>1223</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>387</v>
@@ -28446,7 +28497,7 @@
         <v>1233</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>393</v>
@@ -28480,7 +28531,7 @@
         <v>1225</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>378</v>
@@ -28514,7 +28565,7 @@
         <v>1226</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>387</v>
@@ -28548,7 +28599,7 @@
         <v>1228</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>393</v>
@@ -28582,7 +28633,7 @@
         <v>1236</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>393</v>
@@ -32627,10 +32678,10 @@
         <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1266</v>
+        <v>1283</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1267</v>
+        <v>1284</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -32658,7 +32709,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25.5">
@@ -32669,15 +32720,15 @@
         <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1269</v>
+        <v>1286</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1270</v>
+        <v>1287</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>1271</v>
+        <v>1288</v>
       </c>
       <c r="H8" s="2">
         <v>3</v>
@@ -32700,7 +32751,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25.5">
@@ -32711,15 +32762,15 @@
         <v>85</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1272</v>
+        <v>1289</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1273</v>
+        <v>1290</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>1274</v>
+        <v>1291</v>
       </c>
       <c r="H9" s="2">
         <v>2</v>
@@ -32742,7 +32793,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25.5">
@@ -32753,10 +32804,10 @@
         <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1275</v>
+        <v>1292</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1276</v>
+        <v>1293</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -32784,7 +32835,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25.5">
@@ -32795,15 +32846,15 @@
         <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1277</v>
+        <v>1294</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1278</v>
+        <v>1295</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>1279</v>
+        <v>1296</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -32826,7 +32877,7 @@
         <v>Слабое преимущество</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25.5">
@@ -32837,15 +32888,15 @@
         <v>87</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1280</v>
+        <v>1297</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1281</v>
+        <v>1298</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>1282</v>
+        <v>1299</v>
       </c>
       <c r="H12" s="2">
         <v>4</v>
@@ -32868,7 +32919,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25.5">
@@ -32879,10 +32930,10 @@
         <v>88</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1283</v>
+        <v>1300</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1284</v>
+        <v>1301</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -32910,7 +32961,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25.5">
@@ -32921,15 +32972,15 @@
         <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1285</v>
+        <v>1302</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1286</v>
+        <v>1303</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>1287</v>
+        <v>1304</v>
       </c>
       <c r="H14" s="2">
         <v>5</v>
@@ -32952,7 +33003,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="15" spans="1:14">

--- a/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
+++ b/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-89518d\ЛР5_Анализ_конкурентов\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F7AE98-6B56-41B8-8DFC-25FB36ABA8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B26B893-44CC-4E35-8A5E-E7BD17876EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1322">
   <si>
     <t>Excel-шаблон анализа конкурентов по сайтам</t>
   </si>
@@ -3604,9 +3604,6 @@
     <t>политика конфиденциальности, условия, cookie; страницы безопасности нет</t>
   </si>
   <si>
-    <t>PerfectXL Suite: Risk Finder, Explore, Compare, Highlighter,</t>
-  </si>
-  <si>
     <t>Поиск ошибок формул и аномалий</t>
   </si>
   <si>
@@ -3685,12 +3682,6 @@
     <t>страницы продукта и принципов</t>
   </si>
   <si>
-    <t>Arixcel Explorer: логика формул, сравнение таблиц, карта фор</t>
-  </si>
-  <si>
-    <t>Model Audit, OAK (надстройка Excel), онлайн-курс по моделиро</t>
-  </si>
-  <si>
     <t>Веб-версия без установки</t>
   </si>
   <si>
@@ -3736,9 +3727,6 @@
     <t>страницы безопасности и продукта</t>
   </si>
   <si>
-    <t xml:space="preserve">FinanceOS: FP&amp;A, закрытие месяца, денежные потоки, контроль </t>
-  </si>
-  <si>
     <t>Доказательство вывода детерминированным движком</t>
   </si>
   <si>
@@ -3749,9 +3737,6 @@
   </si>
   <si>
     <t>страница интеграций</t>
-  </si>
-  <si>
-    <t xml:space="preserve">агентная автоматизация аудита, надстройка Excel, извлечение </t>
   </si>
   <si>
     <t>Извлечение данных из документов</t>
@@ -4311,7 +4296,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A414-4B5A-9EA4-A33B837B2866}"/>
+              <c16:uniqueId val="{00000000-4BA2-4D7C-9178-92BC6B3BE678}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4462,7 +4447,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3E41-4EE9-842B-76EDCA87612D}"/>
+              <c16:uniqueId val="{00000000-6E27-4A89-B93E-12C4485FB3A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4499,7 +4484,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3E41-4EE9-842B-76EDCA87612D}"/>
+              <c16:uniqueId val="{00000001-6E27-4A89-B93E-12C4485FB3A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4536,7 +4521,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3E41-4EE9-842B-76EDCA87612D}"/>
+              <c16:uniqueId val="{00000002-6E27-4A89-B93E-12C4485FB3A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4573,7 +4558,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-3E41-4EE9-842B-76EDCA87612D}"/>
+              <c16:uniqueId val="{00000003-6E27-4A89-B93E-12C4485FB3A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4610,7 +4595,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-3E41-4EE9-842B-76EDCA87612D}"/>
+              <c16:uniqueId val="{00000004-6E27-4A89-B93E-12C4485FB3A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4647,7 +4632,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-3E41-4EE9-842B-76EDCA87612D}"/>
+              <c16:uniqueId val="{00000005-6E27-4A89-B93E-12C4485FB3A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4684,7 +4669,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-3E41-4EE9-842B-76EDCA87612D}"/>
+              <c16:uniqueId val="{00000006-6E27-4A89-B93E-12C4485FB3A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10256,12 +10241,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="25.5">
+    <row r="7" spans="1:14" ht="51">
       <c r="A7" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1024</v>
@@ -10270,13 +10255,13 @@
         <v>367</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>1188</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>1189</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -10300,12 +10285,12 @@
       </c>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="25.5">
+    <row r="8" spans="1:14" ht="51">
       <c r="A8" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>1024</v>
@@ -10314,13 +10299,13 @@
         <v>387</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>1191</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -10344,12 +10329,12 @@
       </c>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="25.5">
+    <row r="9" spans="1:14" ht="51">
       <c r="A9" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1024</v>
@@ -10358,13 +10343,13 @@
         <v>387</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>1193</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -10388,12 +10373,12 @@
       </c>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="25.5">
+    <row r="10" spans="1:14" ht="51">
       <c r="A10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>1024</v>
@@ -10402,13 +10387,13 @@
         <v>378</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>1195</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -10432,12 +10417,12 @@
       </c>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="25.5">
+    <row r="11" spans="1:14" ht="51">
       <c r="A11" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>1024</v>
@@ -10446,13 +10431,13 @@
         <v>374</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>1197</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -10476,12 +10461,12 @@
       </c>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="25.5">
+    <row r="12" spans="1:14" ht="51">
       <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>1024</v>
@@ -10490,13 +10475,13 @@
         <v>378</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>1198</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>1199</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -10520,12 +10505,12 @@
       </c>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:14" ht="25.5">
+    <row r="13" spans="1:14" ht="51">
       <c r="A13" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>1024</v>
@@ -10534,13 +10519,13 @@
         <v>378</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>1201</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -10564,12 +10549,12 @@
       </c>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="25.5">
+    <row r="14" spans="1:14" ht="51">
       <c r="A14" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>1024</v>
@@ -10578,13 +10563,13 @@
         <v>378</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>1203</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -10608,12 +10593,12 @@
       </c>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="1:14" ht="25.5">
+    <row r="15" spans="1:14" ht="51">
       <c r="A15" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>1024</v>
@@ -10622,13 +10607,13 @@
         <v>387</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>1205</v>
-      </c>
       <c r="G15" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -10652,12 +10637,12 @@
       </c>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="1:14" ht="25.5">
+    <row r="16" spans="1:14" ht="51">
       <c r="A16" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>1024</v>
@@ -10666,13 +10651,13 @@
         <v>387</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>1207</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -10696,12 +10681,12 @@
       </c>
       <c r="N16" s="2"/>
     </row>
-    <row r="17" spans="1:14" ht="25.5">
+    <row r="17" spans="1:14" ht="51">
       <c r="A17" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>1024</v>
@@ -10710,13 +10695,13 @@
         <v>387</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>1209</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -10740,12 +10725,12 @@
       </c>
       <c r="N17" s="2"/>
     </row>
-    <row r="18" spans="1:14" ht="25.5">
+    <row r="18" spans="1:14" ht="51">
       <c r="A18" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>1024</v>
@@ -10754,13 +10739,13 @@
         <v>387</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -10784,12 +10769,12 @@
       </c>
       <c r="N18" s="2"/>
     </row>
-    <row r="19" spans="1:14" ht="25.5">
+    <row r="19" spans="1:14" ht="51">
       <c r="A19" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1186</v>
+        <v>1029</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>1024</v>
@@ -10798,13 +10783,13 @@
         <v>387</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>1212</v>
-      </c>
       <c r="G19" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -10828,12 +10813,12 @@
       </c>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" spans="1:14" ht="25.5">
+    <row r="20" spans="1:14" ht="38.25">
       <c r="A20" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1213</v>
+        <v>1038</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1034</v>
@@ -10842,13 +10827,13 @@
         <v>367</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>1188</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>1189</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -10872,12 +10857,12 @@
       </c>
       <c r="N20" s="2"/>
     </row>
-    <row r="21" spans="1:14" ht="25.5">
+    <row r="21" spans="1:14" ht="38.25">
       <c r="A21" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1213</v>
+        <v>1038</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>1034</v>
@@ -10886,13 +10871,13 @@
         <v>387</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>1191</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -10916,12 +10901,12 @@
       </c>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="1:14" ht="25.5">
+    <row r="22" spans="1:14" ht="38.25">
       <c r="A22" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1213</v>
+        <v>1038</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>1034</v>
@@ -10930,13 +10915,13 @@
         <v>387</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>1193</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -10960,12 +10945,12 @@
       </c>
       <c r="N22" s="2"/>
     </row>
-    <row r="23" spans="1:14" ht="25.5">
+    <row r="23" spans="1:14" ht="38.25">
       <c r="A23" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1213</v>
+        <v>1038</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>1034</v>
@@ -10974,13 +10959,13 @@
         <v>374</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>1197</v>
-      </c>
       <c r="G23" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -11004,12 +10989,12 @@
       </c>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="1:14" ht="25.5">
+    <row r="24" spans="1:14" ht="38.25">
       <c r="A24" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1213</v>
+        <v>1038</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>1034</v>
@@ -11018,13 +11003,13 @@
         <v>387</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>1205</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -11048,12 +11033,12 @@
       </c>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="1:14" ht="25.5">
+    <row r="25" spans="1:14" ht="38.25">
       <c r="A25" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1213</v>
+        <v>1038</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>1034</v>
@@ -11062,13 +11047,13 @@
         <v>387</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>1209</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -11092,12 +11077,12 @@
       </c>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" ht="25.5">
+    <row r="26" spans="1:14" ht="38.25">
       <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1214</v>
+        <v>1044</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>1040</v>
@@ -11106,13 +11091,13 @@
         <v>367</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>1188</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>1189</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -11136,12 +11121,12 @@
       </c>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" ht="25.5">
+    <row r="27" spans="1:14" ht="38.25">
       <c r="A27" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1214</v>
+        <v>1044</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>1040</v>
@@ -11150,13 +11135,13 @@
         <v>387</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>1191</v>
-      </c>
       <c r="G27" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -11180,12 +11165,12 @@
       </c>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" ht="25.5">
+    <row r="28" spans="1:14" ht="38.25">
       <c r="A28" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1214</v>
+        <v>1044</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>1040</v>
@@ -11194,13 +11179,13 @@
         <v>378</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>1195</v>
-      </c>
       <c r="G28" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -11224,12 +11209,12 @@
       </c>
       <c r="N28" s="2"/>
     </row>
-    <row r="29" spans="1:14" ht="25.5">
+    <row r="29" spans="1:14" ht="38.25">
       <c r="A29" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1214</v>
+        <v>1044</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>1040</v>
@@ -11238,13 +11223,13 @@
         <v>374</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>1197</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -11268,12 +11253,12 @@
       </c>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="1:14" ht="25.5">
+    <row r="30" spans="1:14" ht="38.25">
       <c r="A30" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1214</v>
+        <v>1044</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>1040</v>
@@ -11282,13 +11267,13 @@
         <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>1203</v>
-      </c>
       <c r="G30" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -11312,12 +11297,12 @@
       </c>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" spans="1:14" ht="25.5">
+    <row r="31" spans="1:14" ht="38.25">
       <c r="A31" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1214</v>
+        <v>1044</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>1040</v>
@@ -11326,13 +11311,13 @@
         <v>387</v>
       </c>
       <c r="E31" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>1205</v>
-      </c>
       <c r="G31" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -11356,12 +11341,12 @@
       </c>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="1:14" ht="25.5">
+    <row r="32" spans="1:14" ht="38.25">
       <c r="A32" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1214</v>
+        <v>1044</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>1040</v>
@@ -11370,13 +11355,13 @@
         <v>387</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -11400,12 +11385,12 @@
       </c>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="1:14" ht="25.5">
+    <row r="33" spans="1:14" ht="38.25">
       <c r="A33" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1214</v>
+        <v>1044</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>1040</v>
@@ -11414,13 +11399,13 @@
         <v>387</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>1212</v>
-      </c>
       <c r="G33" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -11458,13 +11443,13 @@
         <v>387</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>1191</v>
-      </c>
       <c r="G34" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -11502,13 +11487,13 @@
         <v>374</v>
       </c>
       <c r="E35" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>1197</v>
-      </c>
       <c r="G35" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -11546,13 +11531,13 @@
         <v>374</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>1070</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -11590,13 +11575,13 @@
         <v>387</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -11634,13 +11619,13 @@
         <v>378</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -11678,13 +11663,13 @@
         <v>378</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>1198</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>1199</v>
-      </c>
       <c r="G39" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
@@ -11722,13 +11707,13 @@
         <v>378</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>1201</v>
-      </c>
       <c r="G40" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H40" s="2">
         <v>1</v>
@@ -11766,13 +11751,13 @@
         <v>387</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>1133</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
@@ -11810,13 +11795,13 @@
         <v>378</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>1203</v>
-      </c>
       <c r="G42" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H42" s="2">
         <v>1</v>
@@ -11854,13 +11839,13 @@
         <v>387</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>1207</v>
-      </c>
       <c r="G43" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H43" s="2">
         <v>1</v>
@@ -11898,13 +11883,13 @@
         <v>393</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H44" s="2">
         <v>1</v>
@@ -11942,13 +11927,13 @@
         <v>387</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H45" s="2">
         <v>1</v>
@@ -11986,13 +11971,13 @@
         <v>378</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H46" s="2">
         <v>1</v>
@@ -12030,13 +12015,13 @@
         <v>387</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H47" s="2">
         <v>1</v>
@@ -12074,13 +12059,13 @@
         <v>393</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H48" s="2">
         <v>1</v>
@@ -12118,13 +12103,13 @@
         <v>374</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>1197</v>
-      </c>
       <c r="G49" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H49" s="2">
         <v>1</v>
@@ -12162,13 +12147,13 @@
         <v>374</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>1070</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H50" s="2">
         <v>1</v>
@@ -12206,13 +12191,13 @@
         <v>387</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H51" s="2">
         <v>1</v>
@@ -12250,13 +12235,13 @@
         <v>378</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>1198</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>1199</v>
-      </c>
       <c r="G52" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H52" s="2">
         <v>1</v>
@@ -12294,13 +12279,13 @@
         <v>378</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>1201</v>
-      </c>
       <c r="G53" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
@@ -12338,13 +12323,13 @@
         <v>387</v>
       </c>
       <c r="E54" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>1205</v>
-      </c>
       <c r="G54" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H54" s="2">
         <v>1</v>
@@ -12382,13 +12367,13 @@
         <v>387</v>
       </c>
       <c r="E55" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>1207</v>
-      </c>
       <c r="G55" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H55" s="2">
         <v>1</v>
@@ -12426,13 +12411,13 @@
         <v>387</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H56" s="2">
         <v>1</v>
@@ -12461,7 +12446,7 @@
         <v>87</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>1059</v>
@@ -12470,13 +12455,13 @@
         <v>378</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>1195</v>
-      </c>
       <c r="G57" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H57" s="2">
         <v>1</v>
@@ -12505,7 +12490,7 @@
         <v>87</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>1059</v>
@@ -12514,13 +12499,13 @@
         <v>374</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>1197</v>
-      </c>
       <c r="G58" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H58" s="2">
         <v>1</v>
@@ -12549,7 +12534,7 @@
         <v>87</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>1059</v>
@@ -12558,13 +12543,13 @@
         <v>374</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>1070</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H59" s="2">
         <v>1</v>
@@ -12593,7 +12578,7 @@
         <v>87</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>1059</v>
@@ -12602,13 +12587,13 @@
         <v>387</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H60" s="2">
         <v>1</v>
@@ -12637,7 +12622,7 @@
         <v>87</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>1059</v>
@@ -12646,13 +12631,13 @@
         <v>393</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H61" s="2">
         <v>1</v>
@@ -12681,7 +12666,7 @@
         <v>87</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>1059</v>
@@ -12690,13 +12675,13 @@
         <v>378</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H62" s="2">
         <v>1</v>
@@ -12725,7 +12710,7 @@
         <v>87</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>1059</v>
@@ -12734,13 +12719,13 @@
         <v>387</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>1133</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H63" s="2">
         <v>1</v>
@@ -12769,7 +12754,7 @@
         <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>1059</v>
@@ -12778,13 +12763,13 @@
         <v>378</v>
       </c>
       <c r="E64" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>1203</v>
-      </c>
       <c r="G64" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H64" s="2">
         <v>1</v>
@@ -12813,7 +12798,7 @@
         <v>87</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>1059</v>
@@ -12822,13 +12807,13 @@
         <v>387</v>
       </c>
       <c r="E65" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>1205</v>
-      </c>
       <c r="G65" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H65" s="2">
         <v>1</v>
@@ -12857,7 +12842,7 @@
         <v>87</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>1059</v>
@@ -12866,13 +12851,13 @@
         <v>387</v>
       </c>
       <c r="E66" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>1207</v>
-      </c>
       <c r="G66" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H66" s="2">
         <v>1</v>
@@ -12901,7 +12886,7 @@
         <v>87</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>1059</v>
@@ -12910,13 +12895,13 @@
         <v>387</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H67" s="2">
         <v>1</v>
@@ -12945,7 +12930,7 @@
         <v>87</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>1059</v>
@@ -12954,13 +12939,13 @@
         <v>393</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H68" s="2">
         <v>1</v>
@@ -12989,7 +12974,7 @@
         <v>87</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>1059</v>
@@ -12998,13 +12983,13 @@
         <v>378</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H69" s="2">
         <v>1</v>
@@ -13033,7 +13018,7 @@
         <v>87</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1230</v>
+        <v>1063</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>1059</v>
@@ -13042,13 +13027,13 @@
         <v>387</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H70" s="2">
         <v>1</v>
@@ -13072,12 +13057,12 @@
       </c>
       <c r="N70" s="2"/>
     </row>
-    <row r="71" spans="1:14" ht="25.5">
+    <row r="71" spans="1:14" ht="38.25">
       <c r="A71" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>1065</v>
@@ -13086,13 +13071,13 @@
         <v>378</v>
       </c>
       <c r="E71" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>1195</v>
-      </c>
       <c r="G71" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H71" s="2">
         <v>1</v>
@@ -13116,12 +13101,12 @@
       </c>
       <c r="N71" s="2"/>
     </row>
-    <row r="72" spans="1:14" ht="25.5">
+    <row r="72" spans="1:14" ht="38.25">
       <c r="A72" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>1065</v>
@@ -13130,13 +13115,13 @@
         <v>374</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>1197</v>
-      </c>
       <c r="G72" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H72" s="2">
         <v>1</v>
@@ -13160,12 +13145,12 @@
       </c>
       <c r="N72" s="2"/>
     </row>
-    <row r="73" spans="1:14" ht="25.5">
+    <row r="73" spans="1:14" ht="38.25">
       <c r="A73" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>1065</v>
@@ -13174,13 +13159,13 @@
         <v>374</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>1070</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H73" s="2">
         <v>1</v>
@@ -13204,12 +13189,12 @@
       </c>
       <c r="N73" s="2"/>
     </row>
-    <row r="74" spans="1:14" ht="25.5">
+    <row r="74" spans="1:14" ht="38.25">
       <c r="A74" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>1065</v>
@@ -13218,13 +13203,13 @@
         <v>387</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H74" s="2">
         <v>1</v>
@@ -13248,12 +13233,12 @@
       </c>
       <c r="N74" s="2"/>
     </row>
-    <row r="75" spans="1:14" ht="25.5">
+    <row r="75" spans="1:14" ht="38.25">
       <c r="A75" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>1065</v>
@@ -13262,13 +13247,13 @@
         <v>393</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H75" s="2">
         <v>1</v>
@@ -13292,12 +13277,12 @@
       </c>
       <c r="N75" s="2"/>
     </row>
-    <row r="76" spans="1:14" ht="25.5">
+    <row r="76" spans="1:14" ht="38.25">
       <c r="A76" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>1065</v>
@@ -13306,13 +13291,13 @@
         <v>378</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H76" s="2">
         <v>1</v>
@@ -13336,12 +13321,12 @@
       </c>
       <c r="N76" s="2"/>
     </row>
-    <row r="77" spans="1:14" ht="25.5">
+    <row r="77" spans="1:14" ht="38.25">
       <c r="A77" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>1065</v>
@@ -13350,13 +13335,13 @@
         <v>387</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>1133</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H77" s="2">
         <v>1</v>
@@ -13380,12 +13365,12 @@
       </c>
       <c r="N77" s="2"/>
     </row>
-    <row r="78" spans="1:14" ht="25.5">
+    <row r="78" spans="1:14" ht="38.25">
       <c r="A78" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>1065</v>
@@ -13394,13 +13379,13 @@
         <v>378</v>
       </c>
       <c r="E78" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>1203</v>
-      </c>
       <c r="G78" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H78" s="2">
         <v>1</v>
@@ -13424,12 +13409,12 @@
       </c>
       <c r="N78" s="2"/>
     </row>
-    <row r="79" spans="1:14" ht="25.5">
+    <row r="79" spans="1:14" ht="38.25">
       <c r="A79" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>1065</v>
@@ -13438,13 +13423,13 @@
         <v>387</v>
       </c>
       <c r="E79" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>1205</v>
-      </c>
       <c r="G79" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H79" s="2">
         <v>1</v>
@@ -13468,12 +13453,12 @@
       </c>
       <c r="N79" s="2"/>
     </row>
-    <row r="80" spans="1:14" ht="25.5">
+    <row r="80" spans="1:14" ht="38.25">
       <c r="A80" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>1065</v>
@@ -13482,13 +13467,13 @@
         <v>387</v>
       </c>
       <c r="E80" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>1207</v>
-      </c>
       <c r="G80" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H80" s="2">
         <v>1</v>
@@ -13512,12 +13497,12 @@
       </c>
       <c r="N80" s="2"/>
     </row>
-    <row r="81" spans="1:14" ht="25.5">
+    <row r="81" spans="1:14" ht="38.25">
       <c r="A81" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>1065</v>
@@ -13526,13 +13511,13 @@
         <v>393</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H81" s="2">
         <v>1</v>
@@ -13556,12 +13541,12 @@
       </c>
       <c r="N81" s="2"/>
     </row>
-    <row r="82" spans="1:14" ht="25.5">
+    <row r="82" spans="1:14" ht="38.25">
       <c r="A82" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>1065</v>
@@ -13570,13 +13555,13 @@
         <v>378</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H82" s="2">
         <v>1</v>
@@ -13600,12 +13585,12 @@
       </c>
       <c r="N82" s="2"/>
     </row>
-    <row r="83" spans="1:14" ht="25.5">
+    <row r="83" spans="1:14" ht="38.25">
       <c r="A83" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>1065</v>
@@ -13614,13 +13599,13 @@
         <v>393</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H83" s="2">
         <v>1</v>
@@ -13644,12 +13629,12 @@
       </c>
       <c r="N83" s="2"/>
     </row>
-    <row r="84" spans="1:14" ht="25.5">
+    <row r="84" spans="1:14" ht="38.25">
       <c r="A84" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1235</v>
+        <v>1068</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>1065</v>
@@ -13658,13 +13643,13 @@
         <v>393</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H84" s="2">
         <v>1</v>
@@ -18708,13 +18693,13 @@
         <v>152</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1188</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>375</v>
@@ -18737,7 +18722,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -18747,13 +18732,13 @@
         <v>153</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>1190</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1191</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>371</v>
@@ -18776,7 +18761,7 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -18786,13 +18771,13 @@
         <v>154</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>1192</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1193</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>371</v>
@@ -18815,7 +18800,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -18825,13 +18810,13 @@
         <v>155</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>1194</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1195</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>371</v>
@@ -18854,7 +18839,7 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -18864,13 +18849,13 @@
         <v>156</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>1196</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1197</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>375</v>
@@ -18893,7 +18878,7 @@
         <v>Минимальный рыночный стандарт</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -18903,10 +18888,10 @@
         <v>157</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>1070</v>
@@ -18932,7 +18917,7 @@
         <v>Переходит в ожидаемую норму</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -18942,13 +18927,13 @@
         <v>158</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>394</v>
@@ -18971,7 +18956,7 @@
         <v>Переходит в ожидаемую норму</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -18981,13 +18966,13 @@
         <v>159</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>394</v>
@@ -19010,7 +18995,7 @@
         <v>Зона дифференциации</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -19020,13 +19005,13 @@
         <v>160</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>375</v>
@@ -19049,7 +19034,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -19059,13 +19044,13 @@
         <v>161</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>1198</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>1199</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>375</v>
@@ -19088,7 +19073,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -19098,13 +19083,13 @@
         <v>162</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>1200</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>1201</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>371</v>
@@ -19127,7 +19112,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -19137,10 +19122,10 @@
         <v>163</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>1133</v>
@@ -19166,7 +19151,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -19176,13 +19161,13 @@
         <v>164</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>1202</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>1203</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>371</v>
@@ -19205,7 +19190,7 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -19215,13 +19200,13 @@
         <v>165</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>1204</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>1205</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>970</v>
@@ -19244,7 +19229,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -19254,13 +19239,13 @@
         <v>166</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>1206</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>1207</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>371</v>
@@ -19283,7 +19268,7 @@
         <v>Конкурентная норма с влиянием на выбор</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -19293,13 +19278,13 @@
         <v>167</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>394</v>
@@ -19322,7 +19307,7 @@
         <v>Зона дифференциации</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -19332,13 +19317,13 @@
         <v>168</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1208</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>1209</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>371</v>
@@ -19361,7 +19346,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -19371,13 +19356,13 @@
         <v>169</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>394</v>
@@ -19400,7 +19385,7 @@
         <v>Зона дифференциации</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -19410,13 +19395,13 @@
         <v>170</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>1211</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1271</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1212</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>371</v>
@@ -19439,7 +19424,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -19449,13 +19434,13 @@
         <v>171</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>970</v>
@@ -19478,7 +19463,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -19488,13 +19473,13 @@
         <v>172</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>970</v>
@@ -19517,7 +19502,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -19527,13 +19512,13 @@
         <v>173</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>375</v>
@@ -19556,7 +19541,7 @@
         <v>Потенциальный обязательный разрыв</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -19566,13 +19551,13 @@
         <v>174</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>371</v>
@@ -19595,7 +19580,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -19605,13 +19590,13 @@
         <v>175</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>371</v>
@@ -19634,7 +19619,7 @@
         <v>Зона усиления ценности</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -19644,13 +19629,13 @@
         <v>176</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>970</v>
@@ -19673,7 +19658,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -23860,10 +23845,10 @@
         <v>366</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>367</v>
@@ -23886,10 +23871,10 @@
         <v>370</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>367</v>
@@ -23912,10 +23897,10 @@
         <v>373</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>374</v>
@@ -23938,10 +23923,10 @@
         <v>377</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>378</v>
@@ -23964,10 +23949,10 @@
         <v>380</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>378</v>
@@ -23990,10 +23975,10 @@
         <v>382</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>378</v>
@@ -24016,7 +24001,7 @@
         <v>384</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>165</v>
@@ -24042,10 +24027,10 @@
         <v>386</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>387</v>
@@ -24068,10 +24053,10 @@
         <v>390</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>387</v>
@@ -24094,10 +24079,10 @@
         <v>392</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>393</v>
@@ -24120,10 +24105,10 @@
         <v>396</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>397</v>
@@ -24146,10 +24131,10 @@
         <v>400</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>401</v>
@@ -27814,10 +27799,10 @@
         <v>537</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>367</v>
@@ -27848,10 +27833,10 @@
         <v>538</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>387</v>
@@ -27882,10 +27867,10 @@
         <v>539</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>387</v>
@@ -27916,10 +27901,10 @@
         <v>540</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>378</v>
@@ -27950,10 +27935,10 @@
         <v>541</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>374</v>
@@ -27984,10 +27969,10 @@
         <v>542</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>374</v>
@@ -28018,10 +28003,10 @@
         <v>543</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>387</v>
@@ -28052,10 +28037,10 @@
         <v>544</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>393</v>
@@ -28086,10 +28071,10 @@
         <v>545</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>378</v>
@@ -28120,10 +28105,10 @@
         <v>546</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>378</v>
@@ -28154,10 +28139,10 @@
         <v>547</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>378</v>
@@ -28188,10 +28173,10 @@
         <v>548</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>387</v>
@@ -28222,10 +28207,10 @@
         <v>549</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>378</v>
@@ -28256,10 +28241,10 @@
         <v>550</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>387</v>
@@ -28290,10 +28275,10 @@
         <v>551</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>387</v>
@@ -28324,10 +28309,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>393</v>
@@ -28358,10 +28343,10 @@
         <v>553</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>387</v>
@@ -28392,10 +28377,10 @@
         <v>554</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>387</v>
@@ -28426,10 +28411,10 @@
         <v>555</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>387</v>
@@ -28460,10 +28445,10 @@
         <v>556</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>387</v>
@@ -28494,10 +28479,10 @@
         <v>557</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>393</v>
@@ -28528,10 +28513,10 @@
         <v>558</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>378</v>
@@ -28562,10 +28547,10 @@
         <v>559</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>387</v>
@@ -28596,10 +28581,10 @@
         <v>560</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>393</v>
@@ -28630,10 +28615,10 @@
         <v>561</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>393</v>
@@ -32678,10 +32663,10 @@
         <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -32709,7 +32694,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25.5">
@@ -32720,15 +32705,15 @@
         <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="H8" s="2">
         <v>3</v>
@@ -32751,7 +32736,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25.5">
@@ -32762,15 +32747,15 @@
         <v>85</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="H9" s="2">
         <v>2</v>
@@ -32793,7 +32778,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25.5">
@@ -32804,10 +32789,10 @@
         <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -32835,7 +32820,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25.5">
@@ -32846,15 +32831,15 @@
         <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -32877,7 +32862,7 @@
         <v>Слабое преимущество</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25.5">
@@ -32888,15 +32873,15 @@
         <v>87</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="H12" s="2">
         <v>4</v>
@@ -32919,7 +32904,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25.5">
@@ -32930,10 +32915,10 @@
         <v>88</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -32961,7 +32946,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25.5">
@@ -32972,15 +32957,15 @@
         <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="H14" s="2">
         <v>5</v>
@@ -33003,7 +32988,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="15" spans="1:14">

--- a/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
+++ b/ЛР5_Анализ_конкурентов/Excel/ЛР5_2_цифровой_товар_Левитт_Кано_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР5_Анализ_конкурентов\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР5_Анализ_конкурентов\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8064A308-048D-4F6B-BCBD-389C7FC00616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821F2E74-C782-4B07-805A-B18964B4FB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1311">
   <si>
     <t>Excel-шаблон анализа конкурентов по сайтам</t>
   </si>
@@ -3806,6 +3806,9 @@
   </si>
   <si>
     <t>освоить продукт без помощи</t>
+  </si>
+  <si>
+    <t>не делать при дефиците ресурсов</t>
   </si>
   <si>
     <t>работать группой</t>
@@ -4260,7 +4263,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F59D-49D5-BD25-EC558622C0AC}"/>
+              <c16:uniqueId val="{00000000-0271-4390-B7D3-94EE0C7B0A53}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4411,7 +4414,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000000-2E2A-450C-9AA0-67E6D6CB610C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4448,7 +4451,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000001-2E2A-450C-9AA0-67E6D6CB610C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4485,7 +4488,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000002-2E2A-450C-9AA0-67E6D6CB610C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4522,7 +4525,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000003-2E2A-450C-9AA0-67E6D6CB610C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4559,7 +4562,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000004-2E2A-450C-9AA0-67E6D6CB610C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4596,7 +4599,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000005-2E2A-450C-9AA0-67E6D6CB610C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4633,7 +4636,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-22E9-406A-86E3-0504545CEBE1}"/>
+              <c16:uniqueId val="{00000006-2E2A-450C-9AA0-67E6D6CB610C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19193,7 +19196,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>1238</v>
+        <v>1254</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -19206,7 +19209,7 @@
         <v>1206</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>1207</v>
@@ -19245,7 +19248,7 @@
         <v>1221</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1222</v>
@@ -19284,7 +19287,7 @@
         <v>1208</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>1209</v>
@@ -19323,7 +19326,7 @@
         <v>1210</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>1209</v>
@@ -19362,7 +19365,7 @@
         <v>1211</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>1212</v>
@@ -19401,7 +19404,7 @@
         <v>1223</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>1224</v>
@@ -19427,7 +19430,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>1240</v>
+        <v>1254</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -19440,7 +19443,7 @@
         <v>1233</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>1234</v>
@@ -19466,7 +19469,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -19479,7 +19482,7 @@
         <v>1225</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>1219</v>
@@ -19518,7 +19521,7 @@
         <v>1226</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>1227</v>
@@ -19557,7 +19560,7 @@
         <v>1228</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>1229</v>
@@ -19596,7 +19599,7 @@
         <v>1236</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>1191</v>
@@ -19622,7 +19625,7 @@
         <v>Не делать при дефиците ресурсов</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -23809,10 +23812,10 @@
         <v>366</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>367</v>
@@ -23835,10 +23838,10 @@
         <v>370</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>367</v>
@@ -23861,10 +23864,10 @@
         <v>373</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>374</v>
@@ -23887,10 +23890,10 @@
         <v>377</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>378</v>
@@ -23913,10 +23916,10 @@
         <v>380</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>378</v>
@@ -23939,10 +23942,10 @@
         <v>382</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>378</v>
@@ -23965,7 +23968,7 @@
         <v>384</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>165</v>
@@ -23991,10 +23994,10 @@
         <v>386</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>387</v>
@@ -24017,10 +24020,10 @@
         <v>390</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>387</v>
@@ -24043,10 +24046,10 @@
         <v>392</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>393</v>
@@ -24069,10 +24072,10 @@
         <v>396</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>397</v>
@@ -24095,10 +24098,10 @@
         <v>400</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>401</v>
@@ -27766,7 +27769,7 @@
         <v>1187</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>367</v>
@@ -27800,7 +27803,7 @@
         <v>1190</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>387</v>
@@ -27834,7 +27837,7 @@
         <v>1192</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>387</v>
@@ -27868,7 +27871,7 @@
         <v>1194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>378</v>
@@ -27902,7 +27905,7 @@
         <v>1196</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>374</v>
@@ -27936,7 +27939,7 @@
         <v>1215</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>374</v>
@@ -27970,7 +27973,7 @@
         <v>1216</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>387</v>
@@ -28004,7 +28007,7 @@
         <v>1231</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>393</v>
@@ -28038,7 +28041,7 @@
         <v>1218</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>378</v>
@@ -28072,7 +28075,7 @@
         <v>1198</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>378</v>
@@ -28106,7 +28109,7 @@
         <v>1200</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>378</v>
@@ -28140,7 +28143,7 @@
         <v>1220</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>387</v>
@@ -28174,7 +28177,7 @@
         <v>1202</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>378</v>
@@ -28208,7 +28211,7 @@
         <v>1204</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>387</v>
@@ -28242,7 +28245,7 @@
         <v>1206</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>387</v>
@@ -28276,7 +28279,7 @@
         <v>1221</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>393</v>
@@ -28310,7 +28313,7 @@
         <v>1208</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>387</v>
@@ -28344,7 +28347,7 @@
         <v>1210</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>387</v>
@@ -28378,7 +28381,7 @@
         <v>1211</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>387</v>
@@ -28412,7 +28415,7 @@
         <v>1223</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>387</v>
@@ -28446,7 +28449,7 @@
         <v>1233</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>393</v>
@@ -28480,7 +28483,7 @@
         <v>1225</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>378</v>
@@ -28514,7 +28517,7 @@
         <v>1226</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>387</v>
@@ -28548,7 +28551,7 @@
         <v>1228</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>393</v>
@@ -28582,7 +28585,7 @@
         <v>1236</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>393</v>
@@ -32627,10 +32630,10 @@
         <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -32658,7 +32661,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25.5">
@@ -32669,15 +32672,15 @@
         <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H8" s="2">
         <v>3</v>
@@ -32700,7 +32703,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25.5">
@@ -32711,15 +32714,15 @@
         <v>85</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H9" s="2">
         <v>2</v>
@@ -32742,7 +32745,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25.5">
@@ -32753,10 +32756,10 @@
         <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -32784,7 +32787,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25.5">
@@ -32795,15 +32798,15 @@
         <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -32826,7 +32829,7 @@
         <v>Слабое преимущество</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25.5">
@@ -32837,15 +32840,15 @@
         <v>87</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H12" s="2">
         <v>4</v>
@@ -32868,7 +32871,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25.5">
@@ -32879,10 +32882,10 @@
         <v>88</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -32910,7 +32913,7 @@
         <v>Сильное преимущество</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25.5">
@@ -32921,15 +32924,15 @@
         <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H14" s="2">
         <v>5</v>
@@ -32952,7 +32955,7 @@
         <v>Потенциальное преимущество</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="15" spans="1:14">
